--- a/DISPO.xlsx
+++ b/DISPO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C3876B9-8605-4F97-BEC7-71C147AC2AA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35927F40-13FA-414D-9A66-C4DFBEC34484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{D5233C47-2897-4F0E-9138-F4B2B2ED9B28}"/>
   </bookViews>

--- a/DISPO.xlsx
+++ b/DISPO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8480C6A9-F3DE-4B24-BEBB-4D0A8F9431AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C188F28C-62B1-488B-B5E8-6761CAB71DA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{D5233C47-2897-4F0E-9138-F4B2B2ED9B28}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="108">
   <si>
     <t xml:space="preserve">Z01 - A VISTA </t>
   </si>
@@ -358,6 +358,12 @@
   </si>
   <si>
     <t>MOCHILA SPORTSTYLE</t>
+  </si>
+  <si>
+    <t>CHALLENGER 6</t>
+  </si>
+  <si>
+    <t>ARTMRF</t>
   </si>
 </sst>
 </file>
@@ -2616,13 +2622,27 @@
       <c r="AM25" s="4"/>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A26" s="5"/>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="3"/>
+      <c r="A26" s="5">
+        <v>13172698</v>
+      </c>
+      <c r="B26" s="5">
+        <v>7268502</v>
+      </c>
+      <c r="C26" s="5">
+        <v>43341472</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F26" s="6">
+        <v>46132</v>
+      </c>
+      <c r="G26" s="3">
+        <v>60</v>
+      </c>
       <c r="H26" s="4"/>
       <c r="I26" s="4"/>
       <c r="J26" s="4"/>
@@ -2635,11 +2655,21 @@
       <c r="Q26" s="4"/>
       <c r="R26" s="4"/>
       <c r="S26" s="4"/>
-      <c r="T26" s="4"/>
-      <c r="U26" s="4"/>
-      <c r="V26" s="4"/>
-      <c r="W26" s="4"/>
-      <c r="X26" s="4"/>
+      <c r="T26" s="4">
+        <v>2</v>
+      </c>
+      <c r="U26" s="4">
+        <v>2</v>
+      </c>
+      <c r="V26" s="4">
+        <v>3</v>
+      </c>
+      <c r="W26" s="4">
+        <v>3</v>
+      </c>
+      <c r="X26" s="4">
+        <v>2</v>
+      </c>
       <c r="Y26" s="4"/>
       <c r="Z26" s="4"/>
       <c r="AA26" s="4"/>

--- a/DISPO.xlsx
+++ b/DISPO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C188F28C-62B1-488B-B5E8-6761CAB71DA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A34981AB-89B6-4F33-9D6B-F21C9FEDC8F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{D5233C47-2897-4F0E-9138-F4B2B2ED9B28}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Planilha2" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DISPO!$A$1:$X$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DISPO!$B$1:$Z$20</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="109">
   <si>
     <t xml:space="preserve">Z01 - A VISTA </t>
   </si>
@@ -195,9 +195,6 @@
     <t>43752263</t>
   </si>
   <si>
-    <t>VERSA</t>
-  </si>
-  <si>
     <t>43407464</t>
   </si>
   <si>
@@ -207,15 +204,9 @@
     <t>ALGBEG</t>
   </si>
   <si>
-    <t>BGMVML</t>
-  </si>
-  <si>
     <t>ARENIT</t>
   </si>
   <si>
-    <t>JOGGING 101 SE</t>
-  </si>
-  <si>
     <t>PRETO</t>
   </si>
   <si>
@@ -364,6 +355,18 @@
   </si>
   <si>
     <t>ARTMRF</t>
+  </si>
+  <si>
+    <t>Nº</t>
+  </si>
+  <si>
+    <t>PEDIDO MÃE</t>
+  </si>
+  <si>
+    <t>SIM</t>
+  </si>
+  <si>
+    <t>NÃO</t>
   </si>
 </sst>
 </file>
@@ -890,167 +893,179 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D63AD4AA-E078-4C28-AB28-3D04A26ABB28}">
-  <dimension ref="A1:AM26"/>
+  <dimension ref="A1:AO26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="8.85546875" style="1"/>
-    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="19" width="3.42578125" customWidth="1"/>
-    <col min="20" max="20" width="4.42578125" customWidth="1"/>
-    <col min="21" max="21" width="5.140625" customWidth="1"/>
-    <col min="22" max="23" width="4.85546875" customWidth="1"/>
-    <col min="24" max="24" width="4.5703125" customWidth="1"/>
-    <col min="25" max="39" width="6.140625" customWidth="1"/>
+    <col min="1" max="1" width="8.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.85546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.85546875" style="1"/>
+    <col min="7" max="7" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5703125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="21" width="3.42578125" customWidth="1"/>
+    <col min="22" max="22" width="4.42578125" customWidth="1"/>
+    <col min="23" max="23" width="5.140625" customWidth="1"/>
+    <col min="24" max="25" width="4.85546875" customWidth="1"/>
+    <col min="26" max="26" width="4.5703125" customWidth="1"/>
+    <col min="27" max="41" width="6.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" s="11" customFormat="1" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:41" s="11" customFormat="1" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="C1" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J1" s="9">
+        <v>28</v>
+      </c>
+      <c r="K1" s="9">
+        <v>29</v>
+      </c>
+      <c r="L1" s="9">
+        <v>30</v>
+      </c>
+      <c r="M1" s="9">
+        <v>31</v>
+      </c>
+      <c r="N1" s="9">
+        <v>32</v>
+      </c>
+      <c r="O1" s="9">
+        <v>33</v>
+      </c>
+      <c r="P1" s="9">
+        <v>34</v>
+      </c>
+      <c r="Q1" s="9">
+        <v>35</v>
+      </c>
+      <c r="R1" s="9">
+        <v>36</v>
+      </c>
+      <c r="S1" s="9">
+        <v>37</v>
+      </c>
+      <c r="T1" s="9">
+        <v>38</v>
+      </c>
+      <c r="U1" s="9">
+        <v>39</v>
+      </c>
+      <c r="V1" s="10">
+        <v>40</v>
+      </c>
+      <c r="W1" s="9">
+        <v>41</v>
+      </c>
+      <c r="X1" s="9">
+        <v>42</v>
+      </c>
+      <c r="Y1" s="9">
+        <v>43</v>
+      </c>
+      <c r="Z1" s="9">
+        <v>44</v>
+      </c>
+      <c r="AA1" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="AB1" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC1" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="AD1" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="AE1" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="AF1" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG1" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH1" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="AI1" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="AJ1" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="H1" s="9">
-        <v>28</v>
-      </c>
-      <c r="I1" s="9">
-        <v>29</v>
-      </c>
-      <c r="J1" s="9">
-        <v>30</v>
-      </c>
-      <c r="K1" s="9">
-        <v>31</v>
-      </c>
-      <c r="L1" s="9">
-        <v>32</v>
-      </c>
-      <c r="M1" s="9">
-        <v>33</v>
-      </c>
-      <c r="N1" s="9">
-        <v>34</v>
-      </c>
-      <c r="O1" s="9">
-        <v>35</v>
-      </c>
-      <c r="P1" s="9">
-        <v>36</v>
-      </c>
-      <c r="Q1" s="9">
-        <v>37</v>
-      </c>
-      <c r="R1" s="9">
-        <v>38</v>
-      </c>
-      <c r="S1" s="9">
-        <v>39</v>
-      </c>
-      <c r="T1" s="10">
-        <v>40</v>
-      </c>
-      <c r="U1" s="9">
-        <v>41</v>
-      </c>
-      <c r="V1" s="9">
-        <v>42</v>
-      </c>
-      <c r="W1" s="9">
-        <v>43</v>
-      </c>
-      <c r="X1" s="9">
-        <v>44</v>
-      </c>
-      <c r="Y1" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="Z1" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="AA1" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AB1" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="AC1" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="AD1" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="AE1" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="AF1" s="9" t="s">
+      <c r="AK1" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="AG1" s="9" t="s">
+      <c r="AL1" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="AH1" s="9" t="s">
+      <c r="AM1" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="AI1" s="9" t="s">
+      <c r="AN1" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="AJ1" s="9" t="s">
+      <c r="AO1" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="AK1" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="AL1" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="AM1" s="9" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="2" spans="1:39" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5">
         <v>12754260</v>
       </c>
-      <c r="B2" s="5">
+      <c r="C2" s="5">
         <v>4991589</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="F2" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F2" s="6">
+      <c r="G2" s="6">
         <v>46117</v>
       </c>
-      <c r="G2" s="3">
+      <c r="H2" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="I2" s="3">
         <v>120</v>
       </c>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
@@ -1058,17 +1073,13 @@
       <c r="N2" s="4"/>
       <c r="O2" s="4"/>
       <c r="P2" s="4"/>
-      <c r="Q2" s="4">
-        <v>1</v>
-      </c>
-      <c r="R2" s="4">
-        <v>1</v>
-      </c>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
       <c r="S2" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T2" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U2" s="4">
         <v>2</v>
@@ -1077,13 +1088,17 @@
         <v>2</v>
       </c>
       <c r="W2" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X2" s="4">
-        <v>1</v>
-      </c>
-      <c r="Y2" s="4"/>
-      <c r="Z2" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="Y2" s="4">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="4">
+        <v>1</v>
+      </c>
       <c r="AA2" s="4"/>
       <c r="AB2" s="4"/>
       <c r="AC2" s="4"/>
@@ -1097,31 +1112,37 @@
       <c r="AK2" s="4"/>
       <c r="AL2" s="4"/>
       <c r="AM2" s="4"/>
-    </row>
-    <row r="3" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN2" s="4"/>
+      <c r="AO2" s="4"/>
+    </row>
+    <row r="3" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5">
         <v>12754702</v>
       </c>
-      <c r="B3" s="5">
+      <c r="C3" s="5">
         <v>4991830</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="D3" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F3" s="6">
+      <c r="E3" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G3" s="6">
         <v>46147</v>
       </c>
-      <c r="G3" s="3">
+      <c r="H3" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="I3" s="3">
         <v>72</v>
       </c>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
@@ -1129,17 +1150,13 @@
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
-      <c r="Q3" s="4">
-        <v>1</v>
-      </c>
-      <c r="R3" s="4">
-        <v>1</v>
-      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
       <c r="S3" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T3" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U3" s="4">
         <v>2</v>
@@ -1148,13 +1165,17 @@
         <v>2</v>
       </c>
       <c r="W3" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X3" s="4">
-        <v>1</v>
-      </c>
-      <c r="Y3" s="4"/>
-      <c r="Z3" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="Y3" s="4">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="4">
+        <v>1</v>
+      </c>
       <c r="AA3" s="4"/>
       <c r="AB3" s="4"/>
       <c r="AC3" s="4"/>
@@ -1168,56 +1189,62 @@
       <c r="AK3" s="4"/>
       <c r="AL3" s="4"/>
       <c r="AM3" s="4"/>
-    </row>
-    <row r="4" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN3" s="4"/>
+      <c r="AO3" s="4"/>
+    </row>
+    <row r="4" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5">
         <v>12754722</v>
       </c>
-      <c r="B4" s="5">
+      <c r="C4" s="5">
         <v>4991874</v>
       </c>
-      <c r="C4" s="5">
+      <c r="D4" s="5">
         <v>43627383</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F4" s="6">
+      <c r="E4" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G4" s="6">
         <v>46147</v>
       </c>
-      <c r="G4" s="3">
+      <c r="H4" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="I4" s="3">
         <v>48</v>
       </c>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
-      <c r="O4" s="4">
-        <v>1</v>
-      </c>
-      <c r="P4" s="4">
-        <v>2</v>
-      </c>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
       <c r="Q4" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R4" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S4" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T4" s="4">
-        <v>1</v>
-      </c>
-      <c r="U4" s="4"/>
-      <c r="V4" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="U4" s="4">
+        <v>2</v>
+      </c>
+      <c r="V4" s="4">
+        <v>1</v>
+      </c>
       <c r="W4" s="4"/>
       <c r="X4" s="4"/>
       <c r="Y4" s="4"/>
@@ -1235,31 +1262,37 @@
       <c r="AK4" s="4"/>
       <c r="AL4" s="4"/>
       <c r="AM4" s="4"/>
-    </row>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN4" s="4"/>
+      <c r="AO4" s="4"/>
+    </row>
+    <row r="5" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5">
         <v>12754713</v>
       </c>
-      <c r="B5" s="5">
+      <c r="C5" s="5">
         <v>4991815</v>
       </c>
-      <c r="C5" s="5">
+      <c r="D5" s="5">
         <v>43407464</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F5" s="6">
+      <c r="G5" s="6">
         <v>46147</v>
       </c>
-      <c r="G5" s="3">
+      <c r="H5" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="I5" s="3">
         <v>36</v>
       </c>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -1268,26 +1301,26 @@
       <c r="O5" s="4"/>
       <c r="P5" s="4"/>
       <c r="Q5" s="4"/>
-      <c r="R5" s="4">
-        <v>1</v>
-      </c>
-      <c r="S5" s="4">
-        <v>2</v>
-      </c>
+      <c r="R5" s="4"/>
+      <c r="S5" s="4"/>
       <c r="T5" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U5" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V5" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W5" s="4">
-        <v>1</v>
-      </c>
-      <c r="X5" s="4"/>
-      <c r="Y5" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="X5" s="4">
+        <v>2</v>
+      </c>
+      <c r="Y5" s="4">
+        <v>1</v>
+      </c>
       <c r="Z5" s="4"/>
       <c r="AA5" s="4"/>
       <c r="AB5" s="4"/>
@@ -1302,31 +1335,37 @@
       <c r="AK5" s="4"/>
       <c r="AL5" s="4"/>
       <c r="AM5" s="4"/>
-    </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN5" s="4"/>
+      <c r="AO5" s="4"/>
+    </row>
+    <row r="6" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5">
         <v>12757419</v>
       </c>
-      <c r="B6" s="5">
+      <c r="C6" s="5">
         <v>4993025</v>
       </c>
-      <c r="C6" s="5">
+      <c r="D6" s="5">
         <v>43409454</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F6" s="6">
+      <c r="E6" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G6" s="6">
         <v>46117</v>
       </c>
-      <c r="G6" s="3">
+      <c r="H6" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="I6" s="3">
         <v>72</v>
       </c>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -1334,26 +1373,26 @@
       <c r="N6" s="4"/>
       <c r="O6" s="4"/>
       <c r="P6" s="4"/>
-      <c r="Q6" s="4">
-        <v>1</v>
-      </c>
-      <c r="R6" s="4">
-        <v>1</v>
-      </c>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="4"/>
       <c r="S6" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T6" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U6" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V6" s="4">
-        <v>2</v>
-      </c>
-      <c r="W6" s="4"/>
-      <c r="X6" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="W6" s="4">
+        <v>2</v>
+      </c>
+      <c r="X6" s="4">
+        <v>2</v>
+      </c>
       <c r="Y6" s="4"/>
       <c r="Z6" s="4"/>
       <c r="AA6" s="4"/>
@@ -1369,58 +1408,64 @@
       <c r="AK6" s="4"/>
       <c r="AL6" s="4"/>
       <c r="AM6" s="4"/>
-    </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN6" s="4"/>
+      <c r="AO6" s="4"/>
+    </row>
+    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5">
         <v>12790465</v>
       </c>
-      <c r="B7" s="5">
+      <c r="C7" s="5">
         <v>5009739</v>
       </c>
-      <c r="C7" s="5">
+      <c r="D7" s="5">
         <v>43632407</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F7" s="6">
+      <c r="E7" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G7" s="6">
         <v>46142</v>
       </c>
-      <c r="G7" s="3">
+      <c r="H7" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="I7" s="3">
         <v>120</v>
       </c>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
-      <c r="N7" s="4">
-        <v>1</v>
-      </c>
-      <c r="O7" s="4">
-        <v>2</v>
-      </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="4"/>
       <c r="P7" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R7" s="4">
         <v>2</v>
       </c>
       <c r="S7" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T7" s="4">
-        <v>1</v>
-      </c>
-      <c r="U7" s="4"/>
-      <c r="V7" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="U7" s="4">
+        <v>1</v>
+      </c>
+      <c r="V7" s="4">
+        <v>1</v>
+      </c>
       <c r="W7" s="4"/>
       <c r="X7" s="4"/>
       <c r="Y7" s="4"/>
@@ -1438,58 +1483,64 @@
       <c r="AK7" s="4"/>
       <c r="AL7" s="4"/>
       <c r="AM7" s="4"/>
-    </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN7" s="4"/>
+      <c r="AO7" s="4"/>
+    </row>
+    <row r="8" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5">
         <v>12791441</v>
       </c>
-      <c r="B8" s="5">
+      <c r="C8" s="5">
         <v>6932240</v>
       </c>
-      <c r="C8" s="5">
+      <c r="D8" s="5">
         <v>43559375</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F8" s="6">
+      <c r="E8" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G8" s="6">
         <v>46142</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="I8" s="3">
         <v>72</v>
       </c>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
-      <c r="N8" s="4">
-        <v>1</v>
-      </c>
-      <c r="O8" s="4">
-        <v>2</v>
-      </c>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4"/>
       <c r="P8" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R8" s="4">
         <v>2</v>
       </c>
       <c r="S8" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T8" s="4">
-        <v>1</v>
-      </c>
-      <c r="U8" s="4"/>
-      <c r="V8" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="U8" s="4">
+        <v>1</v>
+      </c>
+      <c r="V8" s="4">
+        <v>1</v>
+      </c>
       <c r="W8" s="4"/>
       <c r="X8" s="4"/>
       <c r="Y8" s="4"/>
@@ -1507,53 +1558,59 @@
       <c r="AK8" s="4"/>
       <c r="AL8" s="4"/>
       <c r="AM8" s="4"/>
-    </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN8" s="4"/>
+      <c r="AO8" s="4"/>
+    </row>
+    <row r="9" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5">
         <v>12957672</v>
       </c>
-      <c r="B9" s="5">
+      <c r="C9" s="5">
         <v>7021837</v>
       </c>
-      <c r="C9" s="5">
+      <c r="D9" s="5">
         <v>43286101</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F9" s="6">
+      <c r="E9" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G9" s="6">
         <v>46172</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="I9" s="3">
         <v>144</v>
       </c>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
       <c r="N9" s="4"/>
-      <c r="O9" s="4">
-        <v>2</v>
-      </c>
-      <c r="P9" s="4">
-        <v>3</v>
-      </c>
+      <c r="O9" s="4"/>
+      <c r="P9" s="4"/>
       <c r="Q9" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R9" s="4">
         <v>3</v>
       </c>
       <c r="S9" s="4">
-        <v>1</v>
-      </c>
-      <c r="T9" s="4"/>
-      <c r="U9" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="T9" s="4">
+        <v>3</v>
+      </c>
+      <c r="U9" s="4">
+        <v>1</v>
+      </c>
       <c r="V9" s="4"/>
       <c r="W9" s="4"/>
       <c r="X9" s="4"/>
@@ -1572,56 +1629,62 @@
       <c r="AK9" s="4"/>
       <c r="AL9" s="4"/>
       <c r="AM9" s="4"/>
-    </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN9" s="4"/>
+      <c r="AO9" s="4"/>
+    </row>
+    <row r="10" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5">
         <v>13185976</v>
       </c>
-      <c r="B10" s="5">
+      <c r="C10" s="5">
         <v>5245127</v>
       </c>
-      <c r="C10" s="5">
+      <c r="D10" s="5">
         <v>43389459</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F10" s="6">
+      <c r="E10" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G10" s="6">
         <v>46132</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="I10" s="3">
         <v>36</v>
       </c>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
       <c r="N10" s="4"/>
-      <c r="O10" s="4">
-        <v>1</v>
-      </c>
-      <c r="P10" s="4">
-        <v>2</v>
-      </c>
+      <c r="O10" s="4"/>
+      <c r="P10" s="4"/>
       <c r="Q10" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R10" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S10" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T10" s="4">
-        <v>1</v>
-      </c>
-      <c r="U10" s="4"/>
-      <c r="V10" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="U10" s="4">
+        <v>2</v>
+      </c>
+      <c r="V10" s="4">
+        <v>1</v>
+      </c>
       <c r="W10" s="4"/>
       <c r="X10" s="4"/>
       <c r="Y10" s="4"/>
@@ -1639,42 +1702,44 @@
       <c r="AK10" s="4"/>
       <c r="AL10" s="4"/>
       <c r="AM10" s="4"/>
-    </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN10" s="4"/>
+      <c r="AO10" s="4"/>
+    </row>
+    <row r="11" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5">
         <v>13185987</v>
       </c>
-      <c r="B11" s="5">
+      <c r="C11" s="5">
         <v>7283002</v>
       </c>
-      <c r="C11" s="5">
+      <c r="D11" s="5">
         <v>43306412</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F11" s="6">
+      <c r="E11" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G11" s="6">
         <v>46132</v>
       </c>
-      <c r="G11" s="3">
+      <c r="H11" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="I11" s="3">
         <v>24</v>
       </c>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4">
-        <v>1</v>
-      </c>
-      <c r="K11" s="4">
-        <v>1</v>
-      </c>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
       <c r="L11" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M11" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N11" s="4">
         <v>2</v>
@@ -1685,8 +1750,12 @@
       <c r="P11" s="4">
         <v>2</v>
       </c>
-      <c r="Q11" s="4"/>
-      <c r="R11" s="4"/>
+      <c r="Q11" s="4">
+        <v>2</v>
+      </c>
+      <c r="R11" s="4">
+        <v>2</v>
+      </c>
       <c r="S11" s="4"/>
       <c r="T11" s="4"/>
       <c r="U11" s="4"/>
@@ -1708,56 +1777,62 @@
       <c r="AK11" s="4"/>
       <c r="AL11" s="4"/>
       <c r="AM11" s="4"/>
-    </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN11" s="4"/>
+      <c r="AO11" s="4"/>
+    </row>
+    <row r="12" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5">
         <v>13185986</v>
       </c>
-      <c r="B12" s="5">
+      <c r="C12" s="5">
         <v>7283001</v>
       </c>
-      <c r="C12" s="5">
+      <c r="D12" s="5">
         <v>43336749</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F12" s="6">
+      <c r="E12" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G12" s="6">
         <v>46132</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="I12" s="3">
         <v>12</v>
       </c>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
       <c r="J12" s="4"/>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
       <c r="N12" s="4"/>
-      <c r="O12" s="4">
-        <v>1</v>
-      </c>
-      <c r="P12" s="4">
-        <v>3</v>
-      </c>
+      <c r="O12" s="4"/>
+      <c r="P12" s="4"/>
       <c r="Q12" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R12" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S12" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T12" s="4">
-        <v>1</v>
-      </c>
-      <c r="U12" s="4"/>
-      <c r="V12" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="U12" s="4">
+        <v>2</v>
+      </c>
+      <c r="V12" s="4">
+        <v>1</v>
+      </c>
       <c r="W12" s="4"/>
       <c r="X12" s="4"/>
       <c r="Y12" s="4"/>
@@ -1775,52 +1850,58 @@
       <c r="AK12" s="4"/>
       <c r="AL12" s="4"/>
       <c r="AM12" s="4"/>
-    </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN12" s="4"/>
+      <c r="AO12" s="4"/>
+    </row>
+    <row r="13" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5">
         <v>13185988</v>
       </c>
-      <c r="B13" s="5">
+      <c r="C13" s="5">
         <v>7283003</v>
       </c>
-      <c r="C13" s="5">
+      <c r="D13" s="5">
         <v>43213474</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F13" s="6">
+      <c r="E13" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G13" s="6">
         <v>46132</v>
       </c>
-      <c r="G13" s="3">
+      <c r="H13" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="I13" s="3">
         <v>48</v>
       </c>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
       <c r="J13" s="4"/>
-      <c r="K13" s="4">
-        <v>1</v>
-      </c>
-      <c r="L13" s="4">
-        <v>2</v>
-      </c>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
       <c r="M13" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N13" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O13" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P13" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q13" s="4"/>
-      <c r="R13" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>2</v>
+      </c>
+      <c r="R13" s="4">
+        <v>1</v>
+      </c>
       <c r="S13" s="4"/>
       <c r="T13" s="4"/>
       <c r="U13" s="4"/>
@@ -1842,42 +1923,44 @@
       <c r="AK13" s="4"/>
       <c r="AL13" s="4"/>
       <c r="AM13" s="4"/>
-    </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN13" s="4"/>
+      <c r="AO13" s="4"/>
+    </row>
+    <row r="14" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
+        <v>13</v>
+      </c>
+      <c r="B14" s="5">
         <v>13185974</v>
       </c>
-      <c r="B14" s="5">
+      <c r="C14" s="5">
         <v>5245129</v>
       </c>
-      <c r="C14" s="5">
+      <c r="D14" s="5">
         <v>43649393</v>
       </c>
-      <c r="D14" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F14" s="6">
+      <c r="E14" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G14" s="6">
         <v>46132</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="I14" s="3">
         <v>36</v>
       </c>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4">
-        <v>1</v>
-      </c>
-      <c r="K14" s="4">
-        <v>1</v>
-      </c>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
       <c r="L14" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M14" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N14" s="4">
         <v>2</v>
@@ -1888,8 +1971,12 @@
       <c r="P14" s="4">
         <v>2</v>
       </c>
-      <c r="Q14" s="4"/>
-      <c r="R14" s="4"/>
+      <c r="Q14" s="4">
+        <v>2</v>
+      </c>
+      <c r="R14" s="4">
+        <v>2</v>
+      </c>
       <c r="S14" s="4"/>
       <c r="T14" s="4"/>
       <c r="U14" s="4"/>
@@ -1911,55 +1998,61 @@
       <c r="AK14" s="4"/>
       <c r="AL14" s="4"/>
       <c r="AM14" s="4"/>
-    </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN14" s="4"/>
+      <c r="AO14" s="4"/>
+    </row>
+    <row r="15" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5">
         <v>13167977</v>
       </c>
-      <c r="B15" s="5">
+      <c r="C15" s="5">
         <v>5235628</v>
       </c>
-      <c r="C15" s="5">
+      <c r="D15" s="5">
         <v>43632407</v>
       </c>
-      <c r="D15" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F15" s="6">
+      <c r="E15" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G15" s="6">
         <v>46103</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="I15" s="3">
         <v>108</v>
       </c>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
-      <c r="N15" s="4">
-        <v>1</v>
-      </c>
-      <c r="O15" s="4">
-        <v>2</v>
-      </c>
+      <c r="N15" s="4"/>
+      <c r="O15" s="4"/>
       <c r="P15" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q15" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R15" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S15" s="4">
-        <v>1</v>
-      </c>
-      <c r="T15" s="4"/>
-      <c r="U15" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="T15" s="4">
+        <v>2</v>
+      </c>
+      <c r="U15" s="4">
+        <v>1</v>
+      </c>
       <c r="V15" s="4"/>
       <c r="W15" s="4"/>
       <c r="X15" s="4"/>
@@ -1978,56 +2071,62 @@
       <c r="AK15" s="4"/>
       <c r="AL15" s="4"/>
       <c r="AM15" s="4"/>
-    </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN15" s="4"/>
+      <c r="AO15" s="4"/>
+    </row>
+    <row r="16" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
+        <v>15</v>
+      </c>
+      <c r="B16" s="5">
         <v>13159168</v>
       </c>
-      <c r="B16" s="5">
+      <c r="C16" s="5">
         <v>7254752</v>
       </c>
-      <c r="C16" s="5">
+      <c r="D16" s="5">
         <v>43299316</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F16" s="6">
+      <c r="E16" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G16" s="6">
         <v>46104</v>
       </c>
-      <c r="G16" s="3">
+      <c r="H16" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="I16" s="3">
         <v>48</v>
       </c>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
       <c r="N16" s="4"/>
-      <c r="O16" s="4">
-        <v>1</v>
-      </c>
-      <c r="P16" s="4">
-        <v>3</v>
-      </c>
+      <c r="O16" s="4"/>
+      <c r="P16" s="4"/>
       <c r="Q16" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R16" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S16" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T16" s="4">
-        <v>1</v>
-      </c>
-      <c r="U16" s="4"/>
-      <c r="V16" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="U16" s="4">
+        <v>2</v>
+      </c>
+      <c r="V16" s="4">
+        <v>1</v>
+      </c>
       <c r="W16" s="4"/>
       <c r="X16" s="4"/>
       <c r="Y16" s="4"/>
@@ -2045,55 +2144,61 @@
       <c r="AK16" s="4"/>
       <c r="AL16" s="4"/>
       <c r="AM16" s="4"/>
-    </row>
-    <row r="17" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN16" s="4"/>
+      <c r="AO16" s="4"/>
+    </row>
+    <row r="17" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5">
         <v>13167968</v>
       </c>
-      <c r="B17" s="5">
+      <c r="C17" s="5">
         <v>7263895</v>
       </c>
-      <c r="C17" s="5">
+      <c r="D17" s="5">
         <v>43418328</v>
       </c>
-      <c r="D17" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F17" s="6">
+      <c r="E17" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G17" s="6">
         <v>46103</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
+      <c r="I17" s="3">
+        <v>108</v>
+      </c>
       <c r="J17" s="4"/>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
-      <c r="N17" s="4">
-        <v>1</v>
-      </c>
-      <c r="O17" s="4">
-        <v>2</v>
-      </c>
+      <c r="N17" s="4"/>
+      <c r="O17" s="4"/>
       <c r="P17" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R17" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S17" s="4">
-        <v>1</v>
-      </c>
-      <c r="T17" s="4"/>
-      <c r="U17" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="T17" s="4">
+        <v>2</v>
+      </c>
+      <c r="U17" s="4">
+        <v>1</v>
+      </c>
       <c r="V17" s="4"/>
       <c r="W17" s="4"/>
       <c r="X17" s="4"/>
@@ -2112,56 +2217,62 @@
       <c r="AK17" s="4"/>
       <c r="AL17" s="4"/>
       <c r="AM17" s="4"/>
-    </row>
-    <row r="18" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN17" s="4"/>
+      <c r="AO17" s="4"/>
+    </row>
+    <row r="18" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
+        <v>17</v>
+      </c>
+      <c r="B18" s="5">
         <v>13159121</v>
       </c>
-      <c r="B18" s="5">
+      <c r="C18" s="5">
         <v>5226145</v>
       </c>
-      <c r="C18" s="5">
+      <c r="D18" s="5">
         <v>43697386</v>
       </c>
-      <c r="D18" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F18" s="6">
+      <c r="E18" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G18" s="6">
         <v>46104</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="I18" s="3">
         <v>60</v>
       </c>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
       <c r="J18" s="4"/>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
       <c r="N18" s="4"/>
-      <c r="O18" s="4">
-        <v>1</v>
-      </c>
-      <c r="P18" s="4">
-        <v>2</v>
-      </c>
+      <c r="O18" s="4"/>
+      <c r="P18" s="4"/>
       <c r="Q18" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R18" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S18" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T18" s="4">
-        <v>1</v>
-      </c>
-      <c r="U18" s="4"/>
-      <c r="V18" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="U18" s="4">
+        <v>2</v>
+      </c>
+      <c r="V18" s="4">
+        <v>1</v>
+      </c>
       <c r="W18" s="4"/>
       <c r="X18" s="4"/>
       <c r="Y18" s="4"/>
@@ -2179,31 +2290,37 @@
       <c r="AK18" s="4"/>
       <c r="AL18" s="4"/>
       <c r="AM18" s="4"/>
-    </row>
-    <row r="19" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN18" s="4"/>
+      <c r="AO18" s="4"/>
+    </row>
+    <row r="19" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
+        <v>18</v>
+      </c>
+      <c r="B19" s="5">
         <v>13167974</v>
       </c>
-      <c r="B19" s="5">
+      <c r="C19" s="5">
         <v>5235626</v>
       </c>
-      <c r="C19" s="5">
+      <c r="D19" s="5">
         <v>43242437</v>
       </c>
-      <c r="D19" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="F19" s="6">
+      <c r="F19" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G19" s="6">
         <v>46103</v>
       </c>
-      <c r="G19" s="3">
+      <c r="H19" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="I19" s="3">
         <v>48</v>
       </c>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
       <c r="J19" s="4"/>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -2213,26 +2330,26 @@
       <c r="P19" s="4"/>
       <c r="Q19" s="4"/>
       <c r="R19" s="4"/>
-      <c r="S19" s="4">
-        <v>1</v>
-      </c>
-      <c r="T19" s="4">
-        <v>2</v>
-      </c>
+      <c r="S19" s="4"/>
+      <c r="T19" s="4"/>
       <c r="U19" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V19" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W19" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X19" s="4">
-        <v>1</v>
-      </c>
-      <c r="Y19" s="4"/>
-      <c r="Z19" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="Y19" s="4">
+        <v>2</v>
+      </c>
+      <c r="Z19" s="4">
+        <v>1</v>
+      </c>
       <c r="AA19" s="4"/>
       <c r="AB19" s="4"/>
       <c r="AC19" s="4"/>
@@ -2246,31 +2363,37 @@
       <c r="AK19" s="4"/>
       <c r="AL19" s="4"/>
       <c r="AM19" s="4"/>
-    </row>
-    <row r="20" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN19" s="4"/>
+      <c r="AO19" s="4"/>
+    </row>
+    <row r="20" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
+        <v>19</v>
+      </c>
+      <c r="B20" s="5">
         <v>13167975</v>
       </c>
-      <c r="B20" s="5">
+      <c r="C20" s="5">
         <v>5235627</v>
       </c>
-      <c r="C20" s="5">
+      <c r="D20" s="5">
         <v>43358451</v>
       </c>
-      <c r="D20" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F20" s="6">
+      <c r="E20" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G20" s="6">
         <v>46103</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="I20" s="3">
         <v>48</v>
       </c>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
       <c r="J20" s="4"/>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -2280,26 +2403,26 @@
       <c r="P20" s="4"/>
       <c r="Q20" s="4"/>
       <c r="R20" s="4"/>
-      <c r="S20" s="4">
-        <v>1</v>
-      </c>
-      <c r="T20" s="4">
-        <v>2</v>
-      </c>
+      <c r="S20" s="4"/>
+      <c r="T20" s="4"/>
       <c r="U20" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V20" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W20" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X20" s="4">
-        <v>1</v>
-      </c>
-      <c r="Y20" s="4"/>
-      <c r="Z20" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="Y20" s="4">
+        <v>2</v>
+      </c>
+      <c r="Z20" s="4">
+        <v>1</v>
+      </c>
       <c r="AA20" s="4"/>
       <c r="AB20" s="4"/>
       <c r="AC20" s="4"/>
@@ -2313,31 +2436,37 @@
       <c r="AK20" s="4"/>
       <c r="AL20" s="4"/>
       <c r="AM20" s="4"/>
-    </row>
-    <row r="21" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN20" s="4"/>
+      <c r="AO20" s="4"/>
+    </row>
+    <row r="21" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
+        <v>20</v>
+      </c>
+      <c r="B21" s="5">
         <v>13167976</v>
       </c>
-      <c r="B21" s="5">
+      <c r="C21" s="5">
         <v>5060906</v>
       </c>
-      <c r="C21" s="5">
+      <c r="D21" s="5">
         <v>54111405</v>
       </c>
-      <c r="D21" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F21" s="6">
+      <c r="E21" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G21" s="6">
         <v>46172</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="I21" s="3">
         <v>144</v>
       </c>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -2353,26 +2482,26 @@
       <c r="V21" s="4"/>
       <c r="W21" s="4"/>
       <c r="X21" s="4"/>
-      <c r="Y21" s="4">
-        <v>1</v>
-      </c>
-      <c r="Z21" s="4">
-        <v>2</v>
-      </c>
+      <c r="Y21" s="4"/>
+      <c r="Z21" s="4"/>
       <c r="AA21" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AB21" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC21" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD21" s="4">
-        <v>1</v>
-      </c>
-      <c r="AE21" s="4"/>
-      <c r="AF21" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="AE21" s="4">
+        <v>2</v>
+      </c>
+      <c r="AF21" s="4">
+        <v>1</v>
+      </c>
       <c r="AG21" s="4"/>
       <c r="AH21" s="4"/>
       <c r="AI21" s="4"/>
@@ -2380,31 +2509,37 @@
       <c r="AK21" s="4"/>
       <c r="AL21" s="4"/>
       <c r="AM21" s="4"/>
-    </row>
-    <row r="22" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN21" s="4"/>
+      <c r="AO21" s="4"/>
+    </row>
+    <row r="22" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
+        <v>21</v>
+      </c>
+      <c r="B22" s="5">
         <v>13167979</v>
       </c>
-      <c r="B22" s="5">
+      <c r="C22" s="5">
         <v>6874170</v>
       </c>
-      <c r="C22" s="5">
+      <c r="D22" s="5">
         <v>43758365</v>
       </c>
-      <c r="D22" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F22" s="6">
+      <c r="E22" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G22" s="6">
         <v>46142</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="I22" s="3">
         <v>60</v>
       </c>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -2413,20 +2548,20 @@
       <c r="O22" s="4"/>
       <c r="P22" s="4"/>
       <c r="Q22" s="4"/>
-      <c r="R22" s="4">
-        <v>1</v>
-      </c>
-      <c r="S22" s="4">
-        <v>2</v>
-      </c>
+      <c r="R22" s="4"/>
+      <c r="S22" s="4"/>
       <c r="T22" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U22" s="4">
-        <v>1</v>
-      </c>
-      <c r="V22" s="4"/>
-      <c r="W22" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="V22" s="4">
+        <v>2</v>
+      </c>
+      <c r="W22" s="4">
+        <v>1</v>
+      </c>
       <c r="X22" s="4"/>
       <c r="Y22" s="4"/>
       <c r="Z22" s="4"/>
@@ -2443,31 +2578,37 @@
       <c r="AK22" s="4"/>
       <c r="AL22" s="4"/>
       <c r="AM22" s="4"/>
-    </row>
-    <row r="23" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN22" s="4"/>
+      <c r="AO22" s="4"/>
+    </row>
+    <row r="23" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
+        <v>22</v>
+      </c>
+      <c r="B23" s="5">
         <v>13167978</v>
       </c>
-      <c r="B23" s="5">
+      <c r="C23" s="5">
         <v>791970</v>
       </c>
-      <c r="C23" s="5" t="s">
-        <v>100</v>
-      </c>
       <c r="D23" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F23" s="6">
+        <v>97</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G23" s="6">
         <v>46196</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="I23" s="3">
         <v>120</v>
       </c>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -2491,46 +2632,52 @@
       <c r="AD23" s="4"/>
       <c r="AE23" s="4"/>
       <c r="AF23" s="4"/>
-      <c r="AG23" s="4">
-        <v>1</v>
-      </c>
-      <c r="AH23" s="4">
-        <v>2</v>
-      </c>
+      <c r="AG23" s="4"/>
+      <c r="AH23" s="4"/>
       <c r="AI23" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ23" s="4">
-        <v>1</v>
-      </c>
-      <c r="AK23" s="4"/>
-      <c r="AL23" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="AK23" s="4">
+        <v>2</v>
+      </c>
+      <c r="AL23" s="4">
+        <v>1</v>
+      </c>
       <c r="AM23" s="4"/>
-    </row>
-    <row r="24" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AN23" s="4"/>
+      <c r="AO23" s="4"/>
+    </row>
+    <row r="24" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
+        <v>23</v>
+      </c>
+      <c r="B24" s="5">
         <v>13167973</v>
       </c>
-      <c r="B24" s="5">
+      <c r="C24" s="5">
         <v>793473</v>
       </c>
-      <c r="C24" s="5" t="s">
-        <v>102</v>
-      </c>
       <c r="D24" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F24" s="6">
+        <v>99</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G24" s="6">
         <v>46076</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="I24" s="3">
         <v>240</v>
       </c>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
       <c r="J24" s="4"/>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -2559,35 +2706,41 @@
       <c r="AI24" s="4"/>
       <c r="AJ24" s="4"/>
       <c r="AK24" s="4"/>
-      <c r="AL24" s="4" t="s">
+      <c r="AL24" s="4"/>
+      <c r="AM24" s="4"/>
+      <c r="AN24" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="AO24" s="4"/>
+    </row>
+    <row r="25" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A25" s="5">
+        <v>24</v>
+      </c>
+      <c r="B25" s="5">
+        <v>13167972</v>
+      </c>
+      <c r="C25" s="5">
+        <v>1251823</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G25" s="6">
+        <v>46045</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="I25" s="3">
         <v>96</v>
       </c>
-      <c r="AM24" s="4"/>
-    </row>
-    <row r="25" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A25" s="5">
-        <v>13167972</v>
-      </c>
-      <c r="B25" s="5">
-        <v>1251823</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F25" s="6">
-        <v>46045</v>
-      </c>
-      <c r="G25" s="3">
-        <v>96</v>
-      </c>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4"/>
       <c r="J25" s="4"/>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -2615,36 +2768,42 @@
       <c r="AH25" s="4"/>
       <c r="AI25" s="4"/>
       <c r="AJ25" s="4"/>
-      <c r="AK25" s="4" t="s">
-        <v>95</v>
-      </c>
+      <c r="AK25" s="4"/>
       <c r="AL25" s="4"/>
-      <c r="AM25" s="4"/>
-    </row>
-    <row r="26" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AM25" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="AN25" s="4"/>
+      <c r="AO25" s="4"/>
+    </row>
+    <row r="26" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
+        <v>25</v>
+      </c>
+      <c r="B26" s="5">
         <v>13172698</v>
       </c>
-      <c r="B26" s="5">
+      <c r="C26" s="5">
         <v>7268502</v>
       </c>
-      <c r="C26" s="5">
+      <c r="D26" s="5">
         <v>43341472</v>
       </c>
-      <c r="D26" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="F26" s="6">
+      <c r="E26" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G26" s="6">
         <v>46132</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="I26" s="3">
         <v>60</v>
       </c>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
       <c r="J26" s="4"/>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -2655,23 +2814,23 @@
       <c r="Q26" s="4"/>
       <c r="R26" s="4"/>
       <c r="S26" s="4"/>
-      <c r="T26" s="4">
-        <v>2</v>
-      </c>
-      <c r="U26" s="4">
-        <v>2</v>
-      </c>
+      <c r="T26" s="4"/>
+      <c r="U26" s="4"/>
       <c r="V26" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W26" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X26" s="4">
-        <v>2</v>
-      </c>
-      <c r="Y26" s="4"/>
-      <c r="Z26" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="Y26" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z26" s="4">
+        <v>2</v>
+      </c>
       <c r="AA26" s="4"/>
       <c r="AB26" s="4"/>
       <c r="AC26" s="4"/>
@@ -2685,14 +2844,16 @@
       <c r="AK26" s="4"/>
       <c r="AL26" s="4"/>
       <c r="AM26" s="4"/>
+      <c r="AN26" s="4"/>
+      <c r="AO26" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X20" xr:uid="{D63AD4AA-E078-4C28-AB28-3D04A26ABB28}"/>
+  <autoFilter ref="B1:Z20" xr:uid="{D63AD4AA-E078-4C28-AB28-3D04A26ABB28}"/>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="A1">
+  <conditionalFormatting sqref="B1">
     <cfRule type="duplicateValues" dxfId="1" priority="107"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A26">
+  <conditionalFormatting sqref="B2:B26">
     <cfRule type="duplicateValues" dxfId="0" priority="106"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/DISPO.xlsx
+++ b/DISPO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F0F6AA1-1F4C-4A09-9FF4-E0A0BA67588A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90734382-5014-4678-967D-FB09CE4B87D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{D5233C47-2897-4F0E-9138-F4B2B2ED9B28}"/>
   </bookViews>

--- a/DISPO.xlsx
+++ b/DISPO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C07112F-4C11-47E9-B370-D26F60A8D494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E067214F-6196-45E7-8DB8-A5ACF8EDB13F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{D5233C47-2897-4F0E-9138-F4B2B2ED9B28}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Planilha2" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DISPO!$B$1:$AA$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DISPO!$B$1:$AA$6</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="78">
   <si>
     <t xml:space="preserve">Z01 - A VISTA </t>
   </si>
@@ -271,6 +271,9 @@
   </si>
   <si>
     <t>AZABA</t>
+  </si>
+  <si>
+    <t>CZASTE</t>
   </si>
 </sst>
 </file>
@@ -800,7 +803,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D63AD4AA-E078-4C28-AB28-3D04A26ABB28}">
-  <dimension ref="A1:AP46"/>
+  <dimension ref="A1:AP44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" customWidth="1"/>
@@ -1324,10 +1327,10 @@
     </row>
     <row r="7" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B7" s="5">
-        <v>13137556</v>
+        <v>13137557</v>
       </c>
       <c r="C7" s="5">
         <v>5215319</v>
@@ -1342,14 +1345,14 @@
         <v>53</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="H7" s="6">
-        <v>46141</v>
+        <v>46202</v>
       </c>
       <c r="I7" s="6"/>
       <c r="J7" s="3">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -1400,6 +1403,12 @@
       <c r="AO7" s="4"/>
       <c r="AP7" s="4"/>
     </row>
+    <row r="8" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="C8" s="12"/>
+    </row>
+    <row r="9" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="C9" s="12"/>
+    </row>
     <row r="10" spans="1:42" x14ac:dyDescent="0.25">
       <c r="C10" s="12"/>
     </row>
@@ -1505,16 +1514,10 @@
     <row r="44" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C44" s="12"/>
     </row>
-    <row r="45" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C45" s="12"/>
-    </row>
-    <row r="46" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C46" s="12"/>
-    </row>
   </sheetData>
-  <autoFilter ref="B1:AA7" xr:uid="{D63AD4AA-E078-4C28-AB28-3D04A26ABB28}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:AA7">
-      <sortCondition ref="H1:H7"/>
+  <autoFilter ref="B1:AA6" xr:uid="{D63AD4AA-E078-4C28-AB28-3D04A26ABB28}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:AA6">
+      <sortCondition ref="H1:H6"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -1522,7 +1525,7 @@
     <cfRule type="duplicateValues" dxfId="1" priority="107"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:B7">
-    <cfRule type="duplicateValues" dxfId="0" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="112"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/DISPO.xlsx
+++ b/DISPO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93891512-AA73-404C-8C4D-C64EE6DB7CB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F7ABED0-A763-4210-9DF5-44CAEBF09BD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{D5233C47-2897-4F0E-9138-F4B2B2ED9B28}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Planilha2" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DISPO!$B$1:$AA$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DISPO!$B$1:$AA$26</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="104">
   <si>
     <t xml:space="preserve">Z01 - A VISTA </t>
   </si>
@@ -195,15 +195,9 @@
     <t>PTO/PT</t>
   </si>
   <si>
-    <t>CHB/PT</t>
-  </si>
-  <si>
     <t>LAVAND</t>
   </si>
   <si>
-    <t>PASSO</t>
-  </si>
-  <si>
     <t>33/34</t>
   </si>
   <si>
@@ -267,9 +261,6 @@
     <t>VOA 3</t>
   </si>
   <si>
-    <t>EROS 2 INFANTIL</t>
-  </si>
-  <si>
     <t>VERSA</t>
   </si>
   <si>
@@ -282,9 +273,6 @@
     <t>PRETO</t>
   </si>
   <si>
-    <t>SAFIRA</t>
-  </si>
-  <si>
     <t>RUSH</t>
   </si>
   <si>
@@ -327,12 +315,6 @@
     <t>LUMI</t>
   </si>
   <si>
-    <t>DYNAMIC / 343</t>
-  </si>
-  <si>
-    <t>MRHDRD</t>
-  </si>
-  <si>
     <t>MILITR</t>
   </si>
   <si>
@@ -352,12 +334,6 @@
   </si>
   <si>
     <t>LUNAR</t>
-  </si>
-  <si>
-    <t>ATMOS /101</t>
-  </si>
-  <si>
-    <t>ARTPES</t>
   </si>
   <si>
     <t>STREAM INFANTIL</t>
@@ -455,7 +431,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -480,14 +456,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -523,26 +493,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -586,31 +543,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -968,7 +903,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D63AD4AA-E078-4C28-AB28-3D04A26ABB28}">
-  <dimension ref="A1:AP44"/>
+  <dimension ref="A1:AP30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" customWidth="1"/>
@@ -977,7 +912,7 @@
     <col min="5" max="5" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.85546875" style="1" customWidth="1"/>
     <col min="7" max="7" width="8.85546875" style="1"/>
-    <col min="8" max="8" width="12.5703125" style="16" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5703125" style="15" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.5703125" style="1" customWidth="1"/>
     <col min="10" max="10" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="11" max="22" width="3.42578125" customWidth="1"/>
@@ -990,7 +925,7 @@
   <sheetData>
     <row r="1" spans="1:42" s="11" customFormat="1" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>37</v>
@@ -999,13 +934,13 @@
         <v>38</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G1" s="7" t="s">
         <v>39</v>
@@ -1014,7 +949,7 @@
         <v>40</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J1" s="8" t="s">
         <v>41</v>
@@ -1071,49 +1006,49 @@
         <v>44</v>
       </c>
       <c r="AB1" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC1" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="AD1" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="AC1" s="9" t="s">
+      <c r="AE1" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="AD1" s="9" t="s">
+      <c r="AF1" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="AE1" s="9" t="s">
+      <c r="AG1" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="AF1" s="9" t="s">
+      <c r="AH1" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="AG1" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="AH1" s="9" t="s">
-        <v>60</v>
-      </c>
       <c r="AI1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="AK1" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="AJ1" s="9" t="s">
+      <c r="AL1" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="AK1" s="9" t="s">
+      <c r="AM1" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="AL1" s="9" t="s">
+      <c r="AN1" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="AM1" s="9" t="s">
+      <c r="AO1" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="AN1" s="9" t="s">
+      <c r="AP1" s="9" t="s">
         <v>68</v>
-      </c>
-      <c r="AO1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="AP1" s="9" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:42" x14ac:dyDescent="0.25">
@@ -1127,16 +1062,16 @@
         <v>5274741</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E2" s="5">
         <v>43752263</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H2" s="6">
         <v>46147</v>
@@ -1205,16 +1140,16 @@
         <v>5013428</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E3" s="5">
         <v>43632407</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H3" s="6">
         <v>46172</v>
@@ -1272,32 +1207,32 @@
     </row>
     <row r="4" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="B4" s="5">
-        <v>12791194</v>
+        <v>13224179</v>
       </c>
       <c r="C4" s="5">
-        <v>5013559</v>
+        <v>7372755</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="E4" s="5">
-        <v>43608374</v>
+        <v>43667419</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="H4" s="6">
-        <v>46150</v>
+        <v>46162</v>
       </c>
       <c r="I4" s="13"/>
       <c r="J4" s="3">
-        <v>240</v>
+        <v>24</v>
       </c>
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
@@ -1305,29 +1240,39 @@
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
-      <c r="Q4" s="4">
-        <v>1</v>
-      </c>
-      <c r="R4" s="4">
-        <v>2</v>
-      </c>
-      <c r="S4" s="4">
-        <v>3</v>
-      </c>
-      <c r="T4" s="4">
-        <v>3</v>
-      </c>
-      <c r="U4" s="4">
-        <v>2</v>
+      <c r="Q4" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="R4" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S4" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="T4" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="U4" s="4" t="s">
+        <v>101</v>
       </c>
       <c r="V4" s="4">
         <v>1</v>
       </c>
-      <c r="W4" s="4"/>
-      <c r="X4" s="4"/>
-      <c r="Y4" s="4"/>
-      <c r="Z4" s="4"/>
-      <c r="AA4" s="4"/>
+      <c r="W4" s="4">
+        <v>2</v>
+      </c>
+      <c r="X4" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y4" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z4" s="4">
+        <v>2</v>
+      </c>
+      <c r="AA4" s="4">
+        <v>1</v>
+      </c>
       <c r="AB4" s="4"/>
       <c r="AC4" s="4"/>
       <c r="AD4" s="4"/>
@@ -1346,32 +1291,32 @@
     </row>
     <row r="5" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B5" s="5">
-        <v>13224179</v>
+        <v>13224181</v>
       </c>
       <c r="C5" s="5">
-        <v>7372755</v>
+        <v>7372771</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="E5" s="5">
         <v>43667419</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H5" s="6">
-        <v>46162</v>
+        <v>46193</v>
       </c>
       <c r="I5" s="13"/>
       <c r="J5" s="3">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -1380,37 +1325,37 @@
       <c r="O5" s="4"/>
       <c r="P5" s="4"/>
       <c r="Q5" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="R5" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="S5" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="T5" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="U5" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="V5" s="4">
-        <v>1</v>
-      </c>
-      <c r="W5" s="4">
-        <v>2</v>
-      </c>
-      <c r="X5" s="4">
-        <v>3</v>
-      </c>
-      <c r="Y5" s="4">
-        <v>3</v>
-      </c>
-      <c r="Z5" s="4">
-        <v>2</v>
-      </c>
-      <c r="AA5" s="4">
-        <v>1</v>
+        <v>101</v>
+      </c>
+      <c r="R5" s="4">
+        <v>2</v>
+      </c>
+      <c r="S5" s="4">
+        <v>3</v>
+      </c>
+      <c r="T5" s="4">
+        <v>4</v>
+      </c>
+      <c r="U5" s="4">
+        <v>3</v>
+      </c>
+      <c r="V5" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="W5" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="X5" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="Y5" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z5" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="AA5" s="4" t="s">
+        <v>101</v>
       </c>
       <c r="AB5" s="4"/>
       <c r="AC5" s="4"/>
@@ -1430,32 +1375,32 @@
     </row>
     <row r="6" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B6" s="5">
-        <v>13224181</v>
+        <v>13109256</v>
       </c>
       <c r="C6" s="5">
-        <v>7372771</v>
+        <v>5199180</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="E6" s="5">
-        <v>43667419</v>
+        <v>43395156</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>79</v>
       </c>
       <c r="H6" s="6">
-        <v>46193</v>
+        <v>46165</v>
       </c>
       <c r="I6" s="13"/>
       <c r="J6" s="3">
-        <v>48</v>
+        <v>192</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -1463,38 +1408,30 @@
       <c r="N6" s="4"/>
       <c r="O6" s="4"/>
       <c r="P6" s="4"/>
-      <c r="Q6" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="R6" s="4">
-        <v>2</v>
-      </c>
-      <c r="S6" s="4">
-        <v>3</v>
-      </c>
-      <c r="T6" s="4">
-        <v>4</v>
-      </c>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="4"/>
+      <c r="S6" s="4"/>
+      <c r="T6" s="4"/>
       <c r="U6" s="4">
-        <v>3</v>
-      </c>
-      <c r="V6" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="W6" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="X6" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="Y6" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="Z6" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="AA6" s="4" t="s">
-        <v>109</v>
+        <v>1</v>
+      </c>
+      <c r="V6" s="4">
+        <v>1</v>
+      </c>
+      <c r="W6" s="4">
+        <v>2</v>
+      </c>
+      <c r="X6" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y6" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z6" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="4">
+        <v>1</v>
       </c>
       <c r="AB6" s="4"/>
       <c r="AC6" s="4"/>
@@ -1513,33 +1450,33 @@
       <c r="AP6" s="4"/>
     </row>
     <row r="7" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A7" s="5">
-        <v>324</v>
-      </c>
-      <c r="B7" s="5">
-        <v>13224114</v>
+      <c r="A7" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" s="14">
+        <v>12837174</v>
       </c>
       <c r="C7" s="5">
-        <v>5259457</v>
+        <v>5038292</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="E7" s="5">
-        <v>43608374</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>50</v>
+        <v>102</v>
+      </c>
+      <c r="E7" s="14">
+        <v>54104269</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>76</v>
       </c>
       <c r="H7" s="6">
-        <v>46193</v>
+        <v>46158</v>
       </c>
       <c r="I7" s="13"/>
       <c r="J7" s="3">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -1547,39 +1484,25 @@
       <c r="N7" s="4"/>
       <c r="O7" s="4"/>
       <c r="P7" s="4"/>
-      <c r="Q7" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="R7" s="4">
-        <v>1</v>
-      </c>
-      <c r="S7" s="4">
-        <v>2</v>
-      </c>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="4"/>
+      <c r="S7" s="4"/>
       <c r="T7" s="4">
-        <v>3</v>
-      </c>
-      <c r="U7" s="4">
-        <v>3</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="U7" s="4"/>
       <c r="V7" s="4">
-        <v>2</v>
-      </c>
-      <c r="W7" s="4">
-        <v>1</v>
-      </c>
-      <c r="X7" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="Y7" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="Z7" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="AA7" s="4" t="s">
-        <v>109</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="W7" s="4"/>
+      <c r="X7" s="4">
+        <v>4</v>
+      </c>
+      <c r="Y7" s="4"/>
+      <c r="Z7" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="4"/>
       <c r="AB7" s="4"/>
       <c r="AC7" s="4"/>
       <c r="AD7" s="4"/>
@@ -1597,33 +1520,33 @@
       <c r="AP7" s="4"/>
     </row>
     <row r="8" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A8" s="5">
-        <v>325</v>
-      </c>
-      <c r="B8" s="5">
-        <v>13109256</v>
+      <c r="A8" s="14">
+        <v>334</v>
+      </c>
+      <c r="B8" s="14">
+        <v>12757541</v>
       </c>
       <c r="C8" s="5">
-        <v>5199180</v>
+        <v>6913394</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="E8" s="5">
-        <v>43395156</v>
-      </c>
-      <c r="F8" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E8" s="14">
+        <v>43286101</v>
+      </c>
+      <c r="F8" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>83</v>
+      <c r="G8" s="14" t="s">
+        <v>76</v>
       </c>
       <c r="H8" s="6">
-        <v>46165</v>
+        <v>46147</v>
       </c>
       <c r="I8" s="13"/>
       <c r="J8" s="3">
-        <v>192</v>
+        <v>36</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -1631,31 +1554,31 @@
       <c r="N8" s="4"/>
       <c r="O8" s="4"/>
       <c r="P8" s="4"/>
-      <c r="Q8" s="4"/>
-      <c r="R8" s="4"/>
-      <c r="S8" s="4"/>
-      <c r="T8" s="4"/>
+      <c r="Q8" s="4">
+        <v>1</v>
+      </c>
+      <c r="R8" s="4">
+        <v>2</v>
+      </c>
+      <c r="S8" s="4">
+        <v>2</v>
+      </c>
+      <c r="T8" s="4">
+        <v>3</v>
+      </c>
       <c r="U8" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V8" s="4">
         <v>1</v>
       </c>
       <c r="W8" s="4">
-        <v>2</v>
-      </c>
-      <c r="X8" s="4">
-        <v>3</v>
-      </c>
-      <c r="Y8" s="4">
-        <v>3</v>
-      </c>
-      <c r="Z8" s="4">
-        <v>1</v>
-      </c>
-      <c r="AA8" s="4">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="X8" s="4"/>
+      <c r="Y8" s="4"/>
+      <c r="Z8" s="4"/>
+      <c r="AA8" s="4"/>
       <c r="AB8" s="4"/>
       <c r="AC8" s="4"/>
       <c r="AD8" s="4"/>
@@ -1673,33 +1596,33 @@
       <c r="AP8" s="4"/>
     </row>
     <row r="9" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
-        <v>84</v>
+      <c r="A9" s="14">
+        <v>335</v>
       </c>
       <c r="B9" s="14">
-        <v>12837174</v>
+        <v>12757541</v>
       </c>
       <c r="C9" s="5">
-        <v>5038292</v>
+        <v>6913394</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="E9" s="14">
-        <v>54104269</v>
+        <v>43286101</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H9" s="6">
-        <v>46158</v>
+        <v>46147</v>
       </c>
       <c r="I9" s="13"/>
       <c r="J9" s="3">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -1708,23 +1631,29 @@
       <c r="O9" s="4"/>
       <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
-      <c r="R9" s="4"/>
-      <c r="S9" s="4"/>
+      <c r="R9" s="4">
+        <v>1</v>
+      </c>
+      <c r="S9" s="4">
+        <v>3</v>
+      </c>
       <c r="T9" s="4">
-        <v>2</v>
-      </c>
-      <c r="U9" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="U9" s="4">
+        <v>2</v>
+      </c>
       <c r="V9" s="4">
-        <v>5</v>
-      </c>
-      <c r="W9" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="W9" s="4">
+        <v>1</v>
+      </c>
       <c r="X9" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y9" s="4"/>
-      <c r="Z9" s="4">
-        <v>1</v>
-      </c>
+      <c r="Z9" s="4"/>
       <c r="AA9" s="4"/>
       <c r="AB9" s="4"/>
       <c r="AC9" s="4"/>
@@ -1744,7 +1673,7 @@
     </row>
     <row r="10" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A10" s="14">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B10" s="14">
         <v>12757541</v>
@@ -1753,23 +1682,23 @@
         <v>6913394</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="E10" s="14">
-        <v>43286101</v>
+        <v>43927547</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H10" s="6">
         <v>46147</v>
       </c>
       <c r="I10" s="13"/>
       <c r="J10" s="3">
-        <v>120</v>
+        <v>36</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -1820,32 +1749,32 @@
     </row>
     <row r="11" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A11" s="14">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B11" s="14">
-        <v>12757541</v>
+        <v>12757770</v>
       </c>
       <c r="C11" s="5">
-        <v>6913394</v>
+        <v>4993151</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="E11" s="14">
-        <v>43286101</v>
+        <v>43409454</v>
       </c>
       <c r="F11" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="G11" s="14" t="s">
         <v>86</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>79</v>
       </c>
       <c r="H11" s="6">
         <v>46147</v>
       </c>
       <c r="I11" s="13"/>
       <c r="J11" s="3">
-        <v>108</v>
+        <v>12</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -1854,28 +1783,26 @@
       <c r="O11" s="4"/>
       <c r="P11" s="4"/>
       <c r="Q11" s="4"/>
-      <c r="R11" s="4">
-        <v>1</v>
-      </c>
-      <c r="S11" s="4">
-        <v>3</v>
-      </c>
+      <c r="R11" s="4"/>
+      <c r="S11" s="4"/>
       <c r="T11" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U11" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V11" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W11" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X11" s="4">
-        <v>1</v>
-      </c>
-      <c r="Y11" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="Y11" s="4">
+        <v>2</v>
+      </c>
       <c r="Z11" s="4"/>
       <c r="AA11" s="4"/>
       <c r="AB11" s="4"/>
@@ -1896,32 +1823,32 @@
     </row>
     <row r="12" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A12" s="14">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="B12" s="14">
-        <v>12757541</v>
+        <v>12757770</v>
       </c>
       <c r="C12" s="5">
-        <v>6913394</v>
+        <v>4993151</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="E12" s="14">
-        <v>43927547</v>
+        <v>43752263</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H12" s="6">
         <v>46147</v>
       </c>
       <c r="I12" s="13"/>
       <c r="J12" s="3">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1929,31 +1856,31 @@
       <c r="N12" s="4"/>
       <c r="O12" s="4"/>
       <c r="P12" s="4"/>
-      <c r="Q12" s="4">
-        <v>1</v>
-      </c>
-      <c r="R12" s="4">
-        <v>2</v>
-      </c>
-      <c r="S12" s="4">
-        <v>2</v>
-      </c>
-      <c r="T12" s="4">
-        <v>3</v>
-      </c>
+      <c r="Q12" s="4"/>
+      <c r="R12" s="4"/>
+      <c r="S12" s="4"/>
+      <c r="T12" s="4"/>
       <c r="U12" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V12" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W12" s="4">
-        <v>1</v>
-      </c>
-      <c r="X12" s="4"/>
-      <c r="Y12" s="4"/>
-      <c r="Z12" s="4"/>
-      <c r="AA12" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="X12" s="4">
+        <v>2</v>
+      </c>
+      <c r="Y12" s="4">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA12" s="4">
+        <v>1</v>
+      </c>
       <c r="AB12" s="4"/>
       <c r="AC12" s="4"/>
       <c r="AD12" s="4"/>
@@ -1972,32 +1899,32 @@
     </row>
     <row r="13" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A13" s="14">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B13" s="14">
-        <v>12757770</v>
+        <v>13140161</v>
       </c>
       <c r="C13" s="5">
-        <v>4993151</v>
+        <v>7228507</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="E13" s="14">
-        <v>43409454</v>
+        <v>43299316</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H13" s="6">
         <v>46147</v>
       </c>
       <c r="I13" s="13"/>
       <c r="J13" s="3">
-        <v>12</v>
+        <v>108</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -2005,27 +1932,27 @@
       <c r="N13" s="4"/>
       <c r="O13" s="4"/>
       <c r="P13" s="4"/>
-      <c r="Q13" s="4"/>
-      <c r="R13" s="4"/>
-      <c r="S13" s="4"/>
+      <c r="Q13" s="4">
+        <v>1</v>
+      </c>
+      <c r="R13" s="4">
+        <v>2</v>
+      </c>
+      <c r="S13" s="4">
+        <v>3</v>
+      </c>
       <c r="T13" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U13" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V13" s="4">
-        <v>3</v>
-      </c>
-      <c r="W13" s="4">
-        <v>3</v>
-      </c>
-      <c r="X13" s="4">
-        <v>2</v>
-      </c>
-      <c r="Y13" s="4">
-        <v>2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="W13" s="4"/>
+      <c r="X13" s="4"/>
+      <c r="Y13" s="4"/>
       <c r="Z13" s="4"/>
       <c r="AA13" s="4"/>
       <c r="AB13" s="4"/>
@@ -2046,25 +1973,25 @@
     </row>
     <row r="14" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A14" s="14">
-        <v>340</v>
+        <v>388</v>
       </c>
       <c r="B14" s="14">
-        <v>12757770</v>
+        <v>12757545</v>
       </c>
       <c r="C14" s="5">
-        <v>4993151</v>
+        <v>4993104</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E14" s="14">
-        <v>43752263</v>
+        <v>43389459</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="H14" s="6">
         <v>46147</v>
@@ -2083,27 +2010,13 @@
       <c r="R14" s="4"/>
       <c r="S14" s="4"/>
       <c r="T14" s="4"/>
-      <c r="U14" s="4">
-        <v>1</v>
-      </c>
-      <c r="V14" s="4">
-        <v>2</v>
-      </c>
-      <c r="W14" s="4">
-        <v>3</v>
-      </c>
-      <c r="X14" s="4">
-        <v>2</v>
-      </c>
-      <c r="Y14" s="4">
-        <v>1</v>
-      </c>
-      <c r="Z14" s="4">
-        <v>1</v>
-      </c>
-      <c r="AA14" s="4">
-        <v>1</v>
-      </c>
+      <c r="U14" s="4"/>
+      <c r="V14" s="4"/>
+      <c r="W14" s="4"/>
+      <c r="X14" s="4"/>
+      <c r="Y14" s="4"/>
+      <c r="Z14" s="4"/>
+      <c r="AA14" s="4"/>
       <c r="AB14" s="4"/>
       <c r="AC14" s="4"/>
       <c r="AD14" s="4"/>
@@ -2122,32 +2035,32 @@
     </row>
     <row r="15" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A15" s="14">
-        <v>341</v>
+        <v>390</v>
       </c>
       <c r="B15" s="14">
-        <v>13140161</v>
+        <v>12757893</v>
       </c>
       <c r="C15" s="5">
-        <v>7228507</v>
+        <v>4993255</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="E15" s="14">
-        <v>43299316</v>
+        <v>43632407</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="H15" s="6">
-        <v>46147</v>
+        <v>46172</v>
       </c>
       <c r="I15" s="13"/>
       <c r="J15" s="3">
-        <v>108</v>
+        <v>48</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -2155,23 +2068,21 @@
       <c r="N15" s="4"/>
       <c r="O15" s="4"/>
       <c r="P15" s="4"/>
-      <c r="Q15" s="4">
-        <v>1</v>
-      </c>
+      <c r="Q15" s="4"/>
       <c r="R15" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S15" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T15" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U15" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V15" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W15" s="4"/>
       <c r="X15" s="4"/>
@@ -2196,32 +2107,32 @@
     </row>
     <row r="16" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A16" s="14">
-        <v>388</v>
+        <v>409</v>
       </c>
       <c r="B16" s="14">
-        <v>12757545</v>
+        <v>12758052</v>
       </c>
       <c r="C16" s="5">
-        <v>4993104</v>
+        <v>4993370</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E16" s="14">
-        <v>43389459</v>
+        <v>43393460</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="H16" s="6">
-        <v>46147</v>
+        <v>46172</v>
       </c>
       <c r="I16" s="13"/>
       <c r="J16" s="3">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -2230,11 +2141,21 @@
       <c r="O16" s="4"/>
       <c r="P16" s="4"/>
       <c r="Q16" s="4"/>
-      <c r="R16" s="4"/>
-      <c r="S16" s="4"/>
-      <c r="T16" s="4"/>
-      <c r="U16" s="4"/>
-      <c r="V16" s="4"/>
+      <c r="R16" s="4">
+        <v>1</v>
+      </c>
+      <c r="S16" s="4">
+        <v>2</v>
+      </c>
+      <c r="T16" s="4">
+        <v>4</v>
+      </c>
+      <c r="U16" s="4">
+        <v>3</v>
+      </c>
+      <c r="V16" s="4">
+        <v>2</v>
+      </c>
       <c r="W16" s="4"/>
       <c r="X16" s="4"/>
       <c r="Y16" s="4"/>
@@ -2258,32 +2179,32 @@
     </row>
     <row r="17" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A17" s="14">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="B17" s="14">
-        <v>12757893</v>
+        <v>12758063</v>
       </c>
       <c r="C17" s="5">
-        <v>4993255</v>
+        <v>4993371</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E17" s="14">
-        <v>43632407</v>
+        <v>43393460</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="H17" s="6">
         <v>46172</v>
       </c>
       <c r="I17" s="13"/>
       <c r="J17" s="3">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -2330,60 +2251,74 @@
     </row>
     <row r="18" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A18" s="14">
-        <v>409</v>
+        <v>426</v>
       </c>
       <c r="B18" s="14">
-        <v>12758052</v>
+        <v>13263499</v>
       </c>
       <c r="C18" s="5">
-        <v>4993370</v>
+        <v>5274744</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E18" s="14">
-        <v>43393460</v>
+        <v>43395156</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H18" s="6">
-        <v>46172</v>
+        <v>46147</v>
       </c>
       <c r="I18" s="13"/>
       <c r="J18" s="3">
-        <v>12</v>
+        <v>108</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
       <c r="N18" s="4"/>
       <c r="O18" s="4"/>
-      <c r="P18" s="4"/>
-      <c r="Q18" s="4"/>
-      <c r="R18" s="4">
-        <v>1</v>
-      </c>
-      <c r="S18" s="4">
-        <v>2</v>
-      </c>
-      <c r="T18" s="4">
-        <v>4</v>
+      <c r="P18" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q18" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="R18" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S18" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="T18" s="4" t="s">
+        <v>101</v>
       </c>
       <c r="U18" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V18" s="4">
         <v>2</v>
       </c>
-      <c r="W18" s="4"/>
-      <c r="X18" s="4"/>
-      <c r="Y18" s="4"/>
-      <c r="Z18" s="4"/>
-      <c r="AA18" s="4"/>
+      <c r="W18" s="4">
+        <v>3</v>
+      </c>
+      <c r="X18" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y18" s="4">
+        <v>2</v>
+      </c>
+      <c r="Z18" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA18" s="4" t="s">
+        <v>101</v>
+      </c>
       <c r="AB18" s="4"/>
       <c r="AC18" s="4"/>
       <c r="AD18" s="4"/>
@@ -2402,40 +2337,44 @@
     </row>
     <row r="19" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A19" s="14">
-        <v>412</v>
+        <v>427</v>
       </c>
       <c r="B19" s="14">
-        <v>12758063</v>
+        <v>13263552</v>
       </c>
       <c r="C19" s="5">
-        <v>4993371</v>
+        <v>7426389</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="E19" s="14">
-        <v>43393460</v>
+        <v>43667419</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="H19" s="6">
-        <v>46172</v>
+        <v>46147</v>
       </c>
       <c r="I19" s="13"/>
       <c r="J19" s="3">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
       <c r="M19" s="4"/>
       <c r="N19" s="4"/>
       <c r="O19" s="4"/>
-      <c r="P19" s="4"/>
-      <c r="Q19" s="4"/>
+      <c r="P19" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q19" s="4" t="s">
+        <v>101</v>
+      </c>
       <c r="R19" s="4">
         <v>1</v>
       </c>
@@ -2443,7 +2382,7 @@
         <v>2</v>
       </c>
       <c r="T19" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U19" s="4">
         <v>3</v>
@@ -2451,11 +2390,21 @@
       <c r="V19" s="4">
         <v>2</v>
       </c>
-      <c r="W19" s="4"/>
-      <c r="X19" s="4"/>
-      <c r="Y19" s="4"/>
-      <c r="Z19" s="4"/>
-      <c r="AA19" s="4"/>
+      <c r="W19" s="4">
+        <v>1</v>
+      </c>
+      <c r="X19" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="Y19" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z19" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="AA19" s="4" t="s">
+        <v>101</v>
+      </c>
       <c r="AB19" s="4"/>
       <c r="AC19" s="4"/>
       <c r="AD19" s="4"/>
@@ -2474,32 +2423,32 @@
     </row>
     <row r="20" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A20" s="14">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="B20" s="14">
-        <v>13263562</v>
+        <v>13263489</v>
       </c>
       <c r="C20" s="5">
-        <v>7426388</v>
+        <v>5274747</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="E20" s="14">
-        <v>43298343</v>
+        <v>43616206</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H20" s="6">
         <v>46147</v>
       </c>
       <c r="I20" s="13"/>
       <c r="J20" s="3">
-        <v>180</v>
+        <v>48</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -2507,40 +2456,40 @@
       <c r="N20" s="4"/>
       <c r="O20" s="4"/>
       <c r="P20" s="4" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="Q20" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="R20" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="S20" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="T20" s="4" t="s">
-        <v>109</v>
+        <v>101</v>
+      </c>
+      <c r="R20" s="4">
+        <v>1</v>
+      </c>
+      <c r="S20" s="4">
+        <v>2</v>
+      </c>
+      <c r="T20" s="4">
+        <v>3</v>
       </c>
       <c r="U20" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V20" s="4">
         <v>2</v>
       </c>
       <c r="W20" s="4">
-        <v>3</v>
-      </c>
-      <c r="X20" s="4">
-        <v>3</v>
-      </c>
-      <c r="Y20" s="4">
-        <v>2</v>
-      </c>
-      <c r="Z20" s="4">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="X20" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="Y20" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z20" s="4" t="s">
+        <v>101</v>
       </c>
       <c r="AA20" s="4" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="AB20" s="4"/>
       <c r="AC20" s="4"/>
@@ -2560,32 +2509,32 @@
     </row>
     <row r="21" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A21" s="14">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="B21" s="14">
-        <v>13263499</v>
+        <v>13263547</v>
       </c>
       <c r="C21" s="5">
-        <v>5274744</v>
+        <v>7426398</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="E21" s="14">
-        <v>43395156</v>
+        <v>43927547</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H21" s="6">
-        <v>46147</v>
+        <v>46178</v>
       </c>
       <c r="I21" s="13"/>
       <c r="J21" s="3">
-        <v>108</v>
+        <v>48</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -2593,40 +2542,40 @@
       <c r="N21" s="4"/>
       <c r="O21" s="4"/>
       <c r="P21" s="4" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="Q21" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="R21" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="S21" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="T21" s="4" t="s">
-        <v>109</v>
+        <v>101</v>
+      </c>
+      <c r="R21" s="4">
+        <v>1</v>
+      </c>
+      <c r="S21" s="4">
+        <v>2</v>
+      </c>
+      <c r="T21" s="4">
+        <v>3</v>
       </c>
       <c r="U21" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V21" s="4">
         <v>2</v>
       </c>
       <c r="W21" s="4">
-        <v>3</v>
-      </c>
-      <c r="X21" s="4">
-        <v>3</v>
-      </c>
-      <c r="Y21" s="4">
-        <v>2</v>
-      </c>
-      <c r="Z21" s="4">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="X21" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="Y21" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z21" s="4" t="s">
+        <v>101</v>
       </c>
       <c r="AA21" s="4" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="AB21" s="4"/>
       <c r="AC21" s="4"/>
@@ -2646,32 +2595,32 @@
     </row>
     <row r="22" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A22" s="14">
-        <v>427</v>
+        <v>441</v>
       </c>
       <c r="B22" s="14">
-        <v>13263552</v>
+        <v>13263549</v>
       </c>
       <c r="C22" s="5">
-        <v>7426389</v>
+        <v>7426399</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="E22" s="14">
-        <v>43667419</v>
+        <v>43299316</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="H22" s="6">
-        <v>46147</v>
+        <v>46178</v>
       </c>
       <c r="I22" s="13"/>
       <c r="J22" s="3">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -2679,10 +2628,10 @@
       <c r="N22" s="4"/>
       <c r="O22" s="4"/>
       <c r="P22" s="4" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="Q22" s="4" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="R22" s="4">
         <v>1</v>
@@ -2703,16 +2652,16 @@
         <v>1</v>
       </c>
       <c r="X22" s="4" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="Y22" s="4" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="Z22" s="4" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="AA22" s="4" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="AB22" s="4"/>
       <c r="AC22" s="4"/>
@@ -2732,32 +2681,32 @@
     </row>
     <row r="23" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A23" s="14">
-        <v>429</v>
+        <v>442</v>
       </c>
       <c r="B23" s="14">
-        <v>13263489</v>
+        <v>13263498</v>
       </c>
       <c r="C23" s="5">
-        <v>5274747</v>
+        <v>5274759</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E23" s="14">
-        <v>43616206</v>
+        <v>43263432</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="G23" s="14" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H23" s="6">
-        <v>46147</v>
+        <v>46178</v>
       </c>
       <c r="I23" s="13"/>
       <c r="J23" s="3">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -2765,10 +2714,10 @@
       <c r="N23" s="4"/>
       <c r="O23" s="4"/>
       <c r="P23" s="4" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="Q23" s="4" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="R23" s="4">
         <v>1</v>
@@ -2789,16 +2738,16 @@
         <v>1</v>
       </c>
       <c r="X23" s="4" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="Y23" s="4" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="Z23" s="4" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="AA23" s="4" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="AB23" s="4"/>
       <c r="AC23" s="4"/>
@@ -2818,28 +2767,28 @@
     </row>
     <row r="24" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A24" s="14">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="B24" s="14">
-        <v>13263547</v>
+        <v>13263561</v>
       </c>
       <c r="C24" s="5">
-        <v>7426398</v>
+        <v>7426391</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="E24" s="14">
-        <v>43927547</v>
+        <v>43299316</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="H24" s="6">
-        <v>46178</v>
+        <v>46147</v>
       </c>
       <c r="I24" s="13"/>
       <c r="J24" s="3">
@@ -2851,10 +2800,10 @@
       <c r="N24" s="4"/>
       <c r="O24" s="4"/>
       <c r="P24" s="4" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="Q24" s="4" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="R24" s="4">
         <v>1</v>
@@ -2875,16 +2824,16 @@
         <v>1</v>
       </c>
       <c r="X24" s="4" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="Y24" s="4" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="Z24" s="4" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="AA24" s="4" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="AB24" s="4"/>
       <c r="AC24" s="4"/>
@@ -2904,74 +2853,62 @@
     </row>
     <row r="25" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A25" s="14">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="B25" s="14">
-        <v>13263549</v>
+        <v>13263493</v>
       </c>
       <c r="C25" s="5">
-        <v>7426399</v>
+        <v>5274761</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="E25" s="14">
-        <v>43299316</v>
+        <v>43772253</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="G25" s="14" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="H25" s="6">
         <v>46178</v>
       </c>
       <c r="I25" s="13"/>
       <c r="J25" s="3">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
       <c r="M25" s="4"/>
-      <c r="N25" s="4"/>
-      <c r="O25" s="4"/>
-      <c r="P25" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q25" s="4" t="s">
-        <v>109</v>
+      <c r="N25" s="4">
+        <v>1</v>
+      </c>
+      <c r="O25" s="4">
+        <v>1</v>
+      </c>
+      <c r="P25" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q25" s="4">
+        <v>2</v>
       </c>
       <c r="R25" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S25" s="4">
-        <v>2</v>
-      </c>
-      <c r="T25" s="4">
-        <v>3</v>
-      </c>
-      <c r="U25" s="4">
-        <v>3</v>
-      </c>
-      <c r="V25" s="4">
-        <v>2</v>
-      </c>
-      <c r="W25" s="4">
-        <v>1</v>
-      </c>
-      <c r="X25" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="Y25" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="Z25" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="AA25" s="4" t="s">
-        <v>109</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="T25" s="4"/>
+      <c r="U25" s="4"/>
+      <c r="V25" s="4"/>
+      <c r="W25" s="4"/>
+      <c r="X25" s="4"/>
+      <c r="Y25" s="4"/>
+      <c r="Z25" s="4"/>
+      <c r="AA25" s="4"/>
       <c r="AB25" s="4"/>
       <c r="AC25" s="4"/>
       <c r="AD25" s="4"/>
@@ -2990,32 +2927,32 @@
     </row>
     <row r="26" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A26" s="14">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="B26" s="14">
-        <v>13263498</v>
+        <v>13263487</v>
       </c>
       <c r="C26" s="5">
-        <v>5274759</v>
+        <v>5274754</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E26" s="14">
-        <v>43263432</v>
+        <v>43616206</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="H26" s="6">
-        <v>46178</v>
+        <v>46147</v>
       </c>
       <c r="I26" s="13"/>
       <c r="J26" s="3">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -3023,10 +2960,10 @@
       <c r="N26" s="4"/>
       <c r="O26" s="4"/>
       <c r="P26" s="4" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="Q26" s="4" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="R26" s="4">
         <v>1</v>
@@ -3047,16 +2984,16 @@
         <v>1</v>
       </c>
       <c r="X26" s="4" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="Y26" s="4" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="Z26" s="4" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="AA26" s="4" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="AB26" s="4"/>
       <c r="AC26" s="4"/>
@@ -3075,1119 +3012,25 @@
       <c r="AP26" s="4"/>
     </row>
     <row r="27" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A27" s="14">
-        <v>443</v>
-      </c>
-      <c r="B27" s="14">
-        <v>13263561</v>
-      </c>
-      <c r="C27" s="5">
-        <v>7426391</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="E27" s="14">
-        <v>43299316</v>
-      </c>
-      <c r="F27" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="G27" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="H27" s="6">
-        <v>46147</v>
-      </c>
-      <c r="I27" s="13"/>
-      <c r="J27" s="3">
-        <v>48</v>
-      </c>
-      <c r="K27" s="4"/>
-      <c r="L27" s="4"/>
-      <c r="M27" s="4"/>
-      <c r="N27" s="4"/>
-      <c r="O27" s="4"/>
-      <c r="P27" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q27" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="R27" s="4">
-        <v>1</v>
-      </c>
-      <c r="S27" s="4">
-        <v>2</v>
-      </c>
-      <c r="T27" s="4">
-        <v>3</v>
-      </c>
-      <c r="U27" s="4">
-        <v>3</v>
-      </c>
-      <c r="V27" s="4">
-        <v>2</v>
-      </c>
-      <c r="W27" s="4">
-        <v>1</v>
-      </c>
-      <c r="X27" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="Y27" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="Z27" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="AA27" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="AB27" s="4"/>
-      <c r="AC27" s="4"/>
-      <c r="AD27" s="4"/>
-      <c r="AE27" s="4"/>
-      <c r="AF27" s="4"/>
-      <c r="AG27" s="4"/>
-      <c r="AH27" s="4"/>
-      <c r="AI27" s="4"/>
-      <c r="AJ27" s="4"/>
-      <c r="AK27" s="4"/>
-      <c r="AL27" s="4"/>
-      <c r="AM27" s="4"/>
-      <c r="AN27" s="4"/>
-      <c r="AO27" s="4"/>
-      <c r="AP27" s="4"/>
+      <c r="C27" s="12"/>
     </row>
     <row r="28" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A28" s="14">
-        <v>444</v>
-      </c>
-      <c r="B28" s="14">
-        <v>13263560</v>
-      </c>
-      <c r="C28" s="5">
-        <v>7426392</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="E28" s="14">
-        <v>43286101</v>
-      </c>
-      <c r="F28" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="G28" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="H28" s="6">
-        <v>46147</v>
-      </c>
-      <c r="I28" s="13"/>
-      <c r="J28" s="3">
-        <v>48</v>
-      </c>
-      <c r="K28" s="4"/>
-      <c r="L28" s="4"/>
-      <c r="M28" s="4"/>
-      <c r="N28" s="4"/>
-      <c r="O28" s="4"/>
-      <c r="P28" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q28" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="R28" s="4">
-        <v>1</v>
-      </c>
-      <c r="S28" s="4">
-        <v>2</v>
-      </c>
-      <c r="T28" s="4">
-        <v>3</v>
-      </c>
-      <c r="U28" s="4">
-        <v>3</v>
-      </c>
-      <c r="V28" s="4">
-        <v>2</v>
-      </c>
-      <c r="W28" s="4">
-        <v>1</v>
-      </c>
-      <c r="X28" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="Y28" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="Z28" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="AA28" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="AB28" s="4"/>
-      <c r="AC28" s="4"/>
-      <c r="AD28" s="4"/>
-      <c r="AE28" s="4"/>
-      <c r="AF28" s="4"/>
-      <c r="AG28" s="4"/>
-      <c r="AH28" s="4"/>
-      <c r="AI28" s="4"/>
-      <c r="AJ28" s="4"/>
-      <c r="AK28" s="4"/>
-      <c r="AL28" s="4"/>
-      <c r="AM28" s="4"/>
-      <c r="AN28" s="4"/>
-      <c r="AO28" s="4"/>
-      <c r="AP28" s="4"/>
+      <c r="C28" s="12"/>
     </row>
     <row r="29" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A29" s="14">
-        <v>445</v>
-      </c>
-      <c r="B29" s="14">
-        <v>13263491</v>
-      </c>
-      <c r="C29" s="5">
-        <v>5274753</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="E29" s="14">
-        <v>43409454</v>
-      </c>
-      <c r="F29" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="G29" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="H29" s="6">
-        <v>46147</v>
-      </c>
-      <c r="I29" s="13"/>
-      <c r="J29" s="3">
-        <v>60</v>
-      </c>
-      <c r="K29" s="4"/>
-      <c r="L29" s="4"/>
-      <c r="M29" s="4"/>
-      <c r="N29" s="4"/>
-      <c r="O29" s="4"/>
-      <c r="P29" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q29" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="R29" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="S29" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="T29" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="U29" s="4">
-        <v>1</v>
-      </c>
-      <c r="V29" s="4">
-        <v>2</v>
-      </c>
-      <c r="W29" s="4">
-        <v>3</v>
-      </c>
-      <c r="X29" s="4">
-        <v>3</v>
-      </c>
-      <c r="Y29" s="4">
-        <v>2</v>
-      </c>
-      <c r="Z29" s="4">
-        <v>1</v>
-      </c>
-      <c r="AA29" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="AB29" s="4"/>
-      <c r="AC29" s="4"/>
-      <c r="AD29" s="4"/>
-      <c r="AE29" s="4"/>
-      <c r="AF29" s="4"/>
-      <c r="AG29" s="4"/>
-      <c r="AH29" s="4"/>
-      <c r="AI29" s="4"/>
-      <c r="AJ29" s="4"/>
-      <c r="AK29" s="4"/>
-      <c r="AL29" s="4"/>
-      <c r="AM29" s="4"/>
-      <c r="AN29" s="4"/>
-      <c r="AO29" s="4"/>
-      <c r="AP29" s="4"/>
+      <c r="C29" s="12"/>
     </row>
     <row r="30" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A30" s="14">
-        <v>446</v>
-      </c>
-      <c r="B30" s="14">
-        <v>13263493</v>
-      </c>
-      <c r="C30" s="5">
-        <v>5274761</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="E30" s="14">
-        <v>43772253</v>
-      </c>
-      <c r="F30" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="G30" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="H30" s="6">
-        <v>46178</v>
-      </c>
-      <c r="I30" s="13"/>
-      <c r="J30" s="3">
-        <v>36</v>
-      </c>
-      <c r="K30" s="4"/>
-      <c r="L30" s="4"/>
-      <c r="M30" s="4"/>
-      <c r="N30" s="4">
-        <v>1</v>
-      </c>
-      <c r="O30" s="4">
-        <v>1</v>
-      </c>
-      <c r="P30" s="4">
-        <v>2</v>
-      </c>
-      <c r="Q30" s="4">
-        <v>2</v>
-      </c>
-      <c r="R30" s="4">
-        <v>3</v>
-      </c>
-      <c r="S30" s="4">
-        <v>3</v>
-      </c>
-      <c r="T30" s="4"/>
-      <c r="U30" s="4"/>
-      <c r="V30" s="4"/>
-      <c r="W30" s="4"/>
-      <c r="X30" s="4"/>
-      <c r="Y30" s="4"/>
-      <c r="Z30" s="4"/>
-      <c r="AA30" s="4"/>
-      <c r="AB30" s="4"/>
-      <c r="AC30" s="4"/>
-      <c r="AD30" s="4"/>
-      <c r="AE30" s="4"/>
-      <c r="AF30" s="4"/>
-      <c r="AG30" s="4"/>
-      <c r="AH30" s="4"/>
-      <c r="AI30" s="4"/>
-      <c r="AJ30" s="4"/>
-      <c r="AK30" s="4"/>
-      <c r="AL30" s="4"/>
-      <c r="AM30" s="4"/>
-      <c r="AN30" s="4"/>
-      <c r="AO30" s="4"/>
-      <c r="AP30" s="4"/>
-    </row>
-    <row r="31" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A31" s="14">
-        <v>447</v>
-      </c>
-      <c r="B31" s="14">
-        <v>13263487</v>
-      </c>
-      <c r="C31" s="5">
-        <v>5274754</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="E31" s="14">
-        <v>43616206</v>
-      </c>
-      <c r="F31" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="G31" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="H31" s="6">
-        <v>46147</v>
-      </c>
-      <c r="I31" s="13"/>
-      <c r="J31" s="3">
-        <v>48</v>
-      </c>
-      <c r="K31" s="4"/>
-      <c r="L31" s="4"/>
-      <c r="M31" s="4"/>
-      <c r="N31" s="4"/>
-      <c r="O31" s="4"/>
-      <c r="P31" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q31" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="R31" s="4">
-        <v>1</v>
-      </c>
-      <c r="S31" s="4">
-        <v>2</v>
-      </c>
-      <c r="T31" s="4">
-        <v>3</v>
-      </c>
-      <c r="U31" s="4">
-        <v>3</v>
-      </c>
-      <c r="V31" s="4">
-        <v>2</v>
-      </c>
-      <c r="W31" s="4">
-        <v>1</v>
-      </c>
-      <c r="X31" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="Y31" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="Z31" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="AA31" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="AB31" s="4"/>
-      <c r="AC31" s="4"/>
-      <c r="AD31" s="4"/>
-      <c r="AE31" s="4"/>
-      <c r="AF31" s="4"/>
-      <c r="AG31" s="4"/>
-      <c r="AH31" s="4"/>
-      <c r="AI31" s="4"/>
-      <c r="AJ31" s="4"/>
-      <c r="AK31" s="4"/>
-      <c r="AL31" s="4"/>
-      <c r="AM31" s="4"/>
-      <c r="AN31" s="4"/>
-      <c r="AO31" s="4"/>
-      <c r="AP31" s="4"/>
-    </row>
-    <row r="32" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A32" s="14">
-        <v>456</v>
-      </c>
-      <c r="B32" s="14">
-        <v>13172702</v>
-      </c>
-      <c r="C32" s="5">
-        <v>7268503</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="E32" s="14">
-        <v>43299316</v>
-      </c>
-      <c r="F32" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="G32" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="H32" s="6">
-        <v>46172</v>
-      </c>
-      <c r="I32" s="13"/>
-      <c r="J32" s="3">
-        <v>84</v>
-      </c>
-      <c r="K32" s="4"/>
-      <c r="L32" s="4"/>
-      <c r="M32" s="4"/>
-      <c r="N32" s="4"/>
-      <c r="O32" s="4"/>
-      <c r="P32" s="4"/>
-      <c r="Q32" s="4"/>
-      <c r="R32" s="4">
-        <v>1</v>
-      </c>
-      <c r="S32" s="4">
-        <v>3</v>
-      </c>
-      <c r="T32" s="4">
-        <v>3</v>
-      </c>
-      <c r="U32" s="4">
-        <v>3</v>
-      </c>
-      <c r="V32" s="4">
-        <v>2</v>
-      </c>
-      <c r="W32" s="4"/>
-      <c r="X32" s="4"/>
-      <c r="Y32" s="4"/>
-      <c r="Z32" s="4"/>
-      <c r="AA32" s="4"/>
-      <c r="AB32" s="4"/>
-      <c r="AC32" s="4"/>
-      <c r="AD32" s="4"/>
-      <c r="AE32" s="4"/>
-      <c r="AF32" s="4"/>
-      <c r="AG32" s="4"/>
-      <c r="AH32" s="4"/>
-      <c r="AI32" s="4"/>
-      <c r="AJ32" s="4"/>
-      <c r="AK32" s="4"/>
-      <c r="AL32" s="4"/>
-      <c r="AM32" s="4"/>
-      <c r="AN32" s="4"/>
-      <c r="AO32" s="4"/>
-      <c r="AP32" s="4"/>
-    </row>
-    <row r="33" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A33" s="14">
-        <v>467</v>
-      </c>
-      <c r="B33" s="14">
-        <v>13137448</v>
-      </c>
-      <c r="C33" s="5">
-        <v>5215309</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="E33" s="14">
-        <v>43263432</v>
-      </c>
-      <c r="F33" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="G33" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="H33" s="6">
-        <v>46113</v>
-      </c>
-      <c r="I33" s="13"/>
-      <c r="J33" s="3">
-        <v>12</v>
-      </c>
-      <c r="K33" s="4"/>
-      <c r="L33" s="4"/>
-      <c r="M33" s="4"/>
-      <c r="N33" s="4"/>
-      <c r="O33" s="4"/>
-      <c r="P33" s="4"/>
-      <c r="Q33" s="4">
-        <v>1</v>
-      </c>
-      <c r="R33" s="4">
-        <v>2</v>
-      </c>
-      <c r="S33" s="4">
-        <v>3</v>
-      </c>
-      <c r="T33" s="4">
-        <v>3</v>
-      </c>
-      <c r="U33" s="4">
-        <v>2</v>
-      </c>
-      <c r="V33" s="4">
-        <v>1</v>
-      </c>
-      <c r="W33" s="4"/>
-      <c r="X33" s="4"/>
-      <c r="Y33" s="4"/>
-      <c r="Z33" s="4"/>
-      <c r="AA33" s="4"/>
-      <c r="AB33" s="4"/>
-      <c r="AC33" s="4"/>
-      <c r="AD33" s="4"/>
-      <c r="AE33" s="4"/>
-      <c r="AF33" s="4"/>
-      <c r="AG33" s="4"/>
-      <c r="AH33" s="4"/>
-      <c r="AI33" s="4"/>
-      <c r="AJ33" s="4"/>
-      <c r="AK33" s="4"/>
-      <c r="AL33" s="4"/>
-      <c r="AM33" s="4"/>
-      <c r="AN33" s="4"/>
-      <c r="AO33" s="4"/>
-      <c r="AP33" s="4"/>
-    </row>
-    <row r="34" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A34" s="14">
-        <v>468</v>
-      </c>
-      <c r="B34" s="14">
-        <v>13249326</v>
-      </c>
-      <c r="C34" s="5">
-        <v>5269322</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="E34" s="14">
-        <v>43406455</v>
-      </c>
-      <c r="F34" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="G34" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="H34" s="6">
-        <v>46114</v>
-      </c>
-      <c r="I34" s="13"/>
-      <c r="J34" s="3">
-        <v>12</v>
-      </c>
-      <c r="K34" s="4"/>
-      <c r="L34" s="4"/>
-      <c r="M34" s="4"/>
-      <c r="N34" s="4">
-        <v>1</v>
-      </c>
-      <c r="O34" s="4">
-        <v>1</v>
-      </c>
-      <c r="P34" s="4">
-        <v>2</v>
-      </c>
-      <c r="Q34" s="4">
-        <v>2</v>
-      </c>
-      <c r="R34" s="4">
-        <v>2</v>
-      </c>
-      <c r="S34" s="4">
-        <v>2</v>
-      </c>
-      <c r="T34" s="4"/>
-      <c r="U34" s="4"/>
-      <c r="V34" s="4"/>
-      <c r="W34" s="4"/>
-      <c r="X34" s="4"/>
-      <c r="Y34" s="4"/>
-      <c r="Z34" s="4"/>
-      <c r="AA34" s="4"/>
-      <c r="AB34" s="4"/>
-      <c r="AC34" s="4"/>
-      <c r="AD34" s="4"/>
-      <c r="AE34" s="4"/>
-      <c r="AF34" s="4"/>
-      <c r="AG34" s="4"/>
-      <c r="AH34" s="4"/>
-      <c r="AI34" s="4"/>
-      <c r="AJ34" s="4"/>
-      <c r="AK34" s="4"/>
-      <c r="AL34" s="4"/>
-      <c r="AM34" s="4"/>
-      <c r="AN34" s="4"/>
-      <c r="AO34" s="4"/>
-      <c r="AP34" s="4"/>
-    </row>
-    <row r="35" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A35" s="14">
-        <v>469</v>
-      </c>
-      <c r="B35" s="14">
-        <v>13249325</v>
-      </c>
-      <c r="C35" s="5">
-        <v>5269320</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="E35" s="14">
-        <v>43406455</v>
-      </c>
-      <c r="F35" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="G35" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="H35" s="6">
-        <v>46114</v>
-      </c>
-      <c r="I35" s="13"/>
-      <c r="J35" s="3">
-        <v>12</v>
-      </c>
-      <c r="K35" s="4"/>
-      <c r="L35" s="4"/>
-      <c r="M35" s="4"/>
-      <c r="N35" s="4">
-        <v>1</v>
-      </c>
-      <c r="O35" s="4">
-        <v>1</v>
-      </c>
-      <c r="P35" s="4">
-        <v>2</v>
-      </c>
-      <c r="Q35" s="4">
-        <v>2</v>
-      </c>
-      <c r="R35" s="4">
-        <v>2</v>
-      </c>
-      <c r="S35" s="4">
-        <v>2</v>
-      </c>
-      <c r="T35" s="4"/>
-      <c r="U35" s="4"/>
-      <c r="V35" s="4"/>
-      <c r="W35" s="4"/>
-      <c r="X35" s="4"/>
-      <c r="Y35" s="4"/>
-      <c r="Z35" s="4"/>
-      <c r="AA35" s="4"/>
-      <c r="AB35" s="4"/>
-      <c r="AC35" s="4"/>
-      <c r="AD35" s="4"/>
-      <c r="AE35" s="4"/>
-      <c r="AF35" s="4"/>
-      <c r="AG35" s="4"/>
-      <c r="AH35" s="4"/>
-      <c r="AI35" s="4"/>
-      <c r="AJ35" s="4"/>
-      <c r="AK35" s="4"/>
-      <c r="AL35" s="4"/>
-      <c r="AM35" s="4"/>
-      <c r="AN35" s="4"/>
-      <c r="AO35" s="4"/>
-      <c r="AP35" s="4"/>
-    </row>
-    <row r="36" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A36" s="14">
-        <v>470</v>
-      </c>
-      <c r="B36" s="14">
-        <v>13137456</v>
-      </c>
-      <c r="C36" s="5">
-        <v>5215318</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="E36" s="14">
-        <v>43242437</v>
-      </c>
-      <c r="F36" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="G36" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="H36" s="6">
-        <v>46141</v>
-      </c>
-      <c r="I36" s="13"/>
-      <c r="J36" s="3">
-        <v>12</v>
-      </c>
-      <c r="K36" s="4"/>
-      <c r="L36" s="4"/>
-      <c r="M36" s="4"/>
-      <c r="N36" s="4"/>
-      <c r="O36" s="4"/>
-      <c r="P36" s="4"/>
-      <c r="Q36" s="4"/>
-      <c r="R36" s="4"/>
-      <c r="S36" s="4"/>
-      <c r="T36" s="4">
-        <v>1</v>
-      </c>
-      <c r="U36" s="4">
-        <v>1</v>
-      </c>
-      <c r="V36" s="4">
-        <v>2</v>
-      </c>
-      <c r="W36" s="4">
-        <v>2</v>
-      </c>
-      <c r="X36" s="4">
-        <v>2</v>
-      </c>
-      <c r="Y36" s="4">
-        <v>2</v>
-      </c>
-      <c r="Z36" s="4">
-        <v>1</v>
-      </c>
-      <c r="AA36" s="4">
-        <v>1</v>
-      </c>
-      <c r="AB36" s="4"/>
-      <c r="AC36" s="4"/>
-      <c r="AD36" s="4"/>
-      <c r="AE36" s="4"/>
-      <c r="AF36" s="4"/>
-      <c r="AG36" s="4"/>
-      <c r="AH36" s="4"/>
-      <c r="AI36" s="4"/>
-      <c r="AJ36" s="4"/>
-      <c r="AK36" s="4"/>
-      <c r="AL36" s="4"/>
-      <c r="AM36" s="4"/>
-      <c r="AN36" s="4"/>
-      <c r="AO36" s="4"/>
-      <c r="AP36" s="4"/>
-    </row>
-    <row r="37" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A37" s="14">
-        <v>471</v>
-      </c>
-      <c r="B37" s="14">
-        <v>13137556</v>
-      </c>
-      <c r="C37" s="5">
-        <v>5215319</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="E37" s="14">
-        <v>43242437</v>
-      </c>
-      <c r="F37" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="G37" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="H37" s="6">
-        <v>46141</v>
-      </c>
-      <c r="I37" s="13"/>
-      <c r="J37" s="3">
-        <v>12</v>
-      </c>
-      <c r="K37" s="4"/>
-      <c r="L37" s="4"/>
-      <c r="M37" s="4"/>
-      <c r="N37" s="4"/>
-      <c r="O37" s="4"/>
-      <c r="P37" s="4"/>
-      <c r="Q37" s="4"/>
-      <c r="R37" s="4"/>
-      <c r="S37" s="4"/>
-      <c r="T37" s="4">
-        <v>1</v>
-      </c>
-      <c r="U37" s="4">
-        <v>1</v>
-      </c>
-      <c r="V37" s="4">
-        <v>2</v>
-      </c>
-      <c r="W37" s="4">
-        <v>2</v>
-      </c>
-      <c r="X37" s="4">
-        <v>2</v>
-      </c>
-      <c r="Y37" s="4">
-        <v>2</v>
-      </c>
-      <c r="Z37" s="4">
-        <v>1</v>
-      </c>
-      <c r="AA37" s="4">
-        <v>1</v>
-      </c>
-      <c r="AB37" s="4"/>
-      <c r="AC37" s="4"/>
-      <c r="AD37" s="4"/>
-      <c r="AE37" s="4"/>
-      <c r="AF37" s="4"/>
-      <c r="AG37" s="4"/>
-      <c r="AH37" s="4"/>
-      <c r="AI37" s="4"/>
-      <c r="AJ37" s="4"/>
-      <c r="AK37" s="4"/>
-      <c r="AL37" s="4"/>
-      <c r="AM37" s="4"/>
-      <c r="AN37" s="4"/>
-      <c r="AO37" s="4"/>
-      <c r="AP37" s="4"/>
-    </row>
-    <row r="38" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A38" s="14">
-        <v>472</v>
-      </c>
-      <c r="B38" s="14">
-        <v>13249317</v>
-      </c>
-      <c r="C38" s="5">
-        <v>5269321</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="E38" s="14">
-        <v>43406455</v>
-      </c>
-      <c r="F38" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="G38" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="H38" s="15">
-        <v>46114</v>
-      </c>
-      <c r="I38" s="13"/>
-      <c r="J38" s="3">
-        <v>10</v>
-      </c>
-      <c r="K38" s="4"/>
-      <c r="L38" s="4"/>
-      <c r="M38" s="4"/>
-      <c r="N38" s="4">
-        <v>1</v>
-      </c>
-      <c r="O38" s="4">
-        <v>1</v>
-      </c>
-      <c r="P38" s="4">
-        <v>2</v>
-      </c>
-      <c r="Q38" s="4">
-        <v>2</v>
-      </c>
-      <c r="R38" s="4">
-        <v>2</v>
-      </c>
-      <c r="S38" s="4">
-        <v>2</v>
-      </c>
-      <c r="T38" s="4"/>
-      <c r="U38" s="4"/>
-      <c r="V38" s="4"/>
-      <c r="W38" s="4"/>
-      <c r="X38" s="4"/>
-      <c r="Y38" s="4"/>
-      <c r="Z38" s="4"/>
-      <c r="AA38" s="4"/>
-      <c r="AB38" s="4"/>
-      <c r="AC38" s="4"/>
-      <c r="AD38" s="4"/>
-      <c r="AE38" s="4"/>
-      <c r="AF38" s="4"/>
-      <c r="AG38" s="4"/>
-      <c r="AH38" s="4"/>
-      <c r="AI38" s="4"/>
-      <c r="AJ38" s="4"/>
-      <c r="AK38" s="4"/>
-      <c r="AL38" s="4"/>
-      <c r="AM38" s="4"/>
-      <c r="AN38" s="4"/>
-      <c r="AO38" s="4"/>
-      <c r="AP38" s="4"/>
-    </row>
-    <row r="39" spans="1:42" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="17">
-        <v>3410</v>
-      </c>
-      <c r="B39" s="17">
-        <v>13140162</v>
-      </c>
-      <c r="C39" s="18">
-        <v>7228509</v>
-      </c>
-      <c r="D39" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="E39" s="17">
-        <v>43299316</v>
-      </c>
-      <c r="F39" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="G39" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="H39" s="19">
-        <v>46178</v>
-      </c>
-      <c r="I39" s="20"/>
-      <c r="J39" s="21">
-        <v>96</v>
-      </c>
-      <c r="K39" s="22"/>
-      <c r="L39" s="22"/>
-      <c r="M39" s="22"/>
-      <c r="N39" s="22"/>
-      <c r="O39" s="22"/>
-      <c r="P39" s="22"/>
-      <c r="Q39" s="22">
-        <v>1</v>
-      </c>
-      <c r="R39" s="22">
-        <v>2</v>
-      </c>
-      <c r="S39" s="22">
-        <v>3</v>
-      </c>
-      <c r="T39" s="22">
-        <v>3</v>
-      </c>
-      <c r="U39" s="22">
-        <v>2</v>
-      </c>
-      <c r="V39" s="22">
-        <v>1</v>
-      </c>
-      <c r="W39" s="22"/>
-      <c r="X39" s="22"/>
-      <c r="Y39" s="22"/>
-      <c r="Z39" s="22"/>
-      <c r="AA39" s="22"/>
-      <c r="AB39" s="22"/>
-      <c r="AC39" s="22"/>
-      <c r="AD39" s="22"/>
-      <c r="AE39" s="22"/>
-      <c r="AF39" s="22"/>
-      <c r="AG39" s="22"/>
-      <c r="AH39" s="22"/>
-      <c r="AI39" s="22"/>
-      <c r="AJ39" s="22"/>
-      <c r="AK39" s="22"/>
-      <c r="AL39" s="22"/>
-      <c r="AM39" s="22"/>
-      <c r="AN39" s="22"/>
-      <c r="AO39" s="22"/>
-      <c r="AP39" s="22"/>
-    </row>
-    <row r="40" spans="1:42" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="17">
-        <v>3411</v>
-      </c>
-      <c r="B40" s="17">
-        <v>13140163</v>
-      </c>
-      <c r="C40" s="18">
-        <v>7228502</v>
-      </c>
-      <c r="D40" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="E40" s="17">
-        <v>43299316</v>
-      </c>
-      <c r="F40" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="G40" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="H40" s="19">
-        <v>46178</v>
-      </c>
-      <c r="I40" s="20"/>
-      <c r="J40" s="21">
-        <v>96</v>
-      </c>
-      <c r="K40" s="22"/>
-      <c r="L40" s="22"/>
-      <c r="M40" s="22"/>
-      <c r="N40" s="22"/>
-      <c r="O40" s="22"/>
-      <c r="P40" s="22"/>
-      <c r="Q40" s="22">
-        <v>1</v>
-      </c>
-      <c r="R40" s="22">
-        <v>3</v>
-      </c>
-      <c r="S40" s="22">
-        <v>2</v>
-      </c>
-      <c r="T40" s="22">
-        <v>3</v>
-      </c>
-      <c r="U40" s="22">
-        <v>2</v>
-      </c>
-      <c r="V40" s="22">
-        <v>1</v>
-      </c>
-      <c r="W40" s="22"/>
-      <c r="X40" s="22"/>
-      <c r="Y40" s="22"/>
-      <c r="Z40" s="22"/>
-      <c r="AA40" s="22"/>
-      <c r="AB40" s="22"/>
-      <c r="AC40" s="22"/>
-      <c r="AD40" s="22"/>
-      <c r="AE40" s="22"/>
-      <c r="AF40" s="22"/>
-      <c r="AG40" s="22"/>
-      <c r="AH40" s="22"/>
-      <c r="AI40" s="22"/>
-      <c r="AJ40" s="22"/>
-      <c r="AK40" s="22"/>
-      <c r="AL40" s="22"/>
-      <c r="AM40" s="22"/>
-      <c r="AN40" s="22"/>
-      <c r="AO40" s="22"/>
-      <c r="AP40" s="22"/>
-    </row>
-    <row r="41" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="C41" s="12"/>
-    </row>
-    <row r="42" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="C42" s="12"/>
-    </row>
-    <row r="43" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="C43" s="12"/>
-    </row>
-    <row r="44" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="C44" s="12"/>
+      <c r="C30" s="12"/>
     </row>
   </sheetData>
-  <autoFilter ref="B1:AA6" xr:uid="{D63AD4AA-E078-4C28-AB28-3D04A26ABB28}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:AA6">
-      <sortCondition ref="H1:H6"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="B1:AA26" xr:uid="{D63AD4AA-E078-4C28-AB28-3D04A26ABB28}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="B1">
     <cfRule type="duplicateValues" dxfId="1" priority="107"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B8">
-    <cfRule type="duplicateValues" dxfId="0" priority="112"/>
+  <conditionalFormatting sqref="B2:B6">
+    <cfRule type="duplicateValues" dxfId="0" priority="114"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/DISPO.xlsx
+++ b/DISPO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7d52965f3075d7c0/Documentos/GitHub/Catalogo-Olympikus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{87ED6542-5A1E-4B42-B404-31131A61440F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{73BCBA85-7209-48B3-B231-A211E50C2063}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{87ED6542-5A1E-4B42-B404-31131A61440F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28EB013A-8FA7-4C79-8E0F-1DEA214C0A96}"/>
   <bookViews>
     <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D5233C47-2897-4F0E-9138-F4B2B2ED9B28}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="104">
   <si>
     <t xml:space="preserve">Z01 - A VISTA </t>
   </si>
@@ -352,9 +352,6 @@
   </si>
   <si>
     <t>VULTS</t>
-  </si>
-  <si>
-    <t>SIM</t>
   </si>
 </sst>
 </file>
@@ -2879,9 +2876,7 @@
       <c r="H25" s="6">
         <v>46178</v>
       </c>
-      <c r="I25" s="13" t="s">
-        <v>104</v>
-      </c>
+      <c r="I25" s="13"/>
       <c r="J25" s="3">
         <v>36</v>
       </c>

--- a/DISPO.xlsx
+++ b/DISPO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D1420BC-26F3-4D3E-9D1A-5477021E94FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60FBF264-DE53-4081-89A1-21F48B77EDC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{D5233C47-2897-4F0E-9138-F4B2B2ED9B28}"/>
   </bookViews>
@@ -2276,7 +2276,7 @@
         <v>426</v>
       </c>
       <c r="B18" s="14">
-        <v>13263499</v>
+        <v>13263498</v>
       </c>
       <c r="C18" s="18">
         <v>5274745</v>

--- a/DISPO.xlsx
+++ b/DISPO.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7417FD28-1286-4CA7-AC76-DD6BA06897CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4250A88F-8C9D-4B20-A2C9-12D4EAB86D60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{D5233C47-2897-4F0E-9138-F4B2B2ED9B28}"/>
   </bookViews>
@@ -288,21 +288,12 @@
     <t>SERENO</t>
   </si>
   <si>
-    <t>ATMOS</t>
-  </si>
-  <si>
     <t>DAY</t>
   </si>
   <si>
     <t>CHUMBO</t>
   </si>
   <si>
-    <t>EROS 2</t>
-  </si>
-  <si>
-    <t>BRANCO</t>
-  </si>
-  <si>
     <t>ACQUA</t>
   </si>
   <si>
@@ -346,6 +337,15 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>NUVEM</t>
+  </si>
+  <si>
+    <t>LUNCHB</t>
+  </si>
+  <si>
+    <t>RYLMHO</t>
   </si>
   <si>
     <t>AZABA</t>
@@ -431,7 +431,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -459,12 +459,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -564,7 +558,7 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -924,12 +918,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D63AD4AA-E078-4C28-AB28-3D04A26ABB28}">
-  <dimension ref="A1:AP30"/>
+  <dimension ref="A1:AP53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="8.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.85546875" style="1" customWidth="1"/>
     <col min="7" max="7" width="8.85546875" style="1"/>
@@ -1262,19 +1257,19 @@
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
       <c r="Q4" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="S4" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="U4" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="V4" s="4">
         <v>1</v>
@@ -1346,7 +1341,7 @@
       <c r="O5" s="4"/>
       <c r="P5" s="4"/>
       <c r="Q5" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="R5" s="4">
         <v>2</v>
@@ -1361,22 +1356,22 @@
         <v>3</v>
       </c>
       <c r="V5" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="W5" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="X5" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="Y5" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="Z5" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="AA5" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="AB5" s="4"/>
       <c r="AC5" s="4"/>
@@ -1421,7 +1416,7 @@
       </c>
       <c r="I6" s="13"/>
       <c r="J6" s="3">
-        <v>192</v>
+        <v>228</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -1542,7 +1537,7 @@
     </row>
     <row r="8" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A8" s="14">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B8" s="14">
         <v>12757541</v>
@@ -1554,13 +1549,13 @@
         <v>103</v>
       </c>
       <c r="E8" s="14">
-        <v>43286101</v>
+        <v>43927547</v>
       </c>
       <c r="F8" s="14" t="s">
         <v>82</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H8" s="6">
         <v>46147</v>
@@ -1618,32 +1613,32 @@
     </row>
     <row r="9" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A9" s="14">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="B9" s="14">
-        <v>12757541</v>
+        <v>13140161</v>
       </c>
       <c r="C9" s="5">
-        <v>6913394</v>
+        <v>7228507</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>103</v>
       </c>
       <c r="E9" s="14">
-        <v>43286101</v>
+        <v>43299316</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H9" s="6">
         <v>46147</v>
       </c>
       <c r="I9" s="13"/>
       <c r="J9" s="3">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -1651,9 +1646,11 @@
       <c r="N9" s="4"/>
       <c r="O9" s="4"/>
       <c r="P9" s="4"/>
-      <c r="Q9" s="4"/>
+      <c r="Q9" s="4">
+        <v>1</v>
+      </c>
       <c r="R9" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S9" s="4">
         <v>3</v>
@@ -1667,12 +1664,8 @@
       <c r="V9" s="4">
         <v>1</v>
       </c>
-      <c r="W9" s="4">
-        <v>1</v>
-      </c>
-      <c r="X9" s="4">
-        <v>1</v>
-      </c>
+      <c r="W9" s="4"/>
+      <c r="X9" s="4"/>
       <c r="Y9" s="4"/>
       <c r="Z9" s="4"/>
       <c r="AA9" s="4"/>
@@ -1694,32 +1687,32 @@
     </row>
     <row r="10" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A10" s="14">
-        <v>336</v>
+        <v>388</v>
       </c>
       <c r="B10" s="14">
-        <v>12757541</v>
+        <v>12757545</v>
       </c>
       <c r="C10" s="5">
-        <v>6913394</v>
+        <v>4993104</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E10" s="14">
-        <v>43927547</v>
+        <v>43389459</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="H10" s="6">
         <v>46147</v>
       </c>
       <c r="I10" s="13"/>
       <c r="J10" s="3">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -1727,27 +1720,13 @@
       <c r="N10" s="4"/>
       <c r="O10" s="4"/>
       <c r="P10" s="4"/>
-      <c r="Q10" s="4">
-        <v>1</v>
-      </c>
-      <c r="R10" s="4">
-        <v>2</v>
-      </c>
-      <c r="S10" s="4">
-        <v>2</v>
-      </c>
-      <c r="T10" s="4">
-        <v>3</v>
-      </c>
-      <c r="U10" s="4">
-        <v>2</v>
-      </c>
-      <c r="V10" s="4">
-        <v>1</v>
-      </c>
-      <c r="W10" s="4">
-        <v>1</v>
-      </c>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="4"/>
+      <c r="S10" s="4"/>
+      <c r="T10" s="4"/>
+      <c r="U10" s="4"/>
+      <c r="V10" s="4"/>
+      <c r="W10" s="4"/>
       <c r="X10" s="4"/>
       <c r="Y10" s="4"/>
       <c r="Z10" s="4"/>
@@ -1770,32 +1749,32 @@
     </row>
     <row r="11" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A11" s="14">
-        <v>339</v>
+        <v>390</v>
       </c>
       <c r="B11" s="14">
-        <v>12757770</v>
+        <v>12757893</v>
       </c>
       <c r="C11" s="5">
-        <v>4993151</v>
+        <v>4993255</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>102</v>
       </c>
       <c r="E11" s="14">
-        <v>43409454</v>
+        <v>43632407</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>86</v>
+        <v>51</v>
       </c>
       <c r="H11" s="6">
-        <v>46147</v>
+        <v>46172</v>
       </c>
       <c r="I11" s="13"/>
       <c r="J11" s="3">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -1804,26 +1783,24 @@
       <c r="O11" s="4"/>
       <c r="P11" s="4"/>
       <c r="Q11" s="4"/>
-      <c r="R11" s="4"/>
-      <c r="S11" s="4"/>
+      <c r="R11" s="4">
+        <v>1</v>
+      </c>
+      <c r="S11" s="4">
+        <v>2</v>
+      </c>
       <c r="T11" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U11" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V11" s="4">
-        <v>3</v>
-      </c>
-      <c r="W11" s="4">
-        <v>3</v>
-      </c>
-      <c r="X11" s="4">
-        <v>2</v>
-      </c>
-      <c r="Y11" s="4">
-        <v>2</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="W11" s="4"/>
+      <c r="X11" s="4"/>
+      <c r="Y11" s="4"/>
       <c r="Z11" s="4"/>
       <c r="AA11" s="4"/>
       <c r="AB11" s="4"/>
@@ -1844,28 +1821,28 @@
     </row>
     <row r="12" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A12" s="14">
-        <v>340</v>
+        <v>409</v>
       </c>
       <c r="B12" s="14">
-        <v>12757770</v>
+        <v>12758052</v>
       </c>
       <c r="C12" s="5">
-        <v>4993151</v>
+        <v>4993370</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>102</v>
       </c>
       <c r="E12" s="14">
-        <v>43752263</v>
+        <v>43393460</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="H12" s="6">
-        <v>46147</v>
+        <v>46172</v>
       </c>
       <c r="I12" s="13"/>
       <c r="J12" s="3">
@@ -1878,30 +1855,26 @@
       <c r="O12" s="4"/>
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
-      <c r="R12" s="4"/>
-      <c r="S12" s="4"/>
-      <c r="T12" s="4"/>
+      <c r="R12" s="4">
+        <v>1</v>
+      </c>
+      <c r="S12" s="4">
+        <v>2</v>
+      </c>
+      <c r="T12" s="4">
+        <v>4</v>
+      </c>
       <c r="U12" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V12" s="4">
         <v>2</v>
       </c>
-      <c r="W12" s="4">
-        <v>3</v>
-      </c>
-      <c r="X12" s="4">
-        <v>2</v>
-      </c>
-      <c r="Y12" s="4">
-        <v>1</v>
-      </c>
-      <c r="Z12" s="4">
-        <v>1</v>
-      </c>
-      <c r="AA12" s="4">
-        <v>1</v>
-      </c>
+      <c r="W12" s="4"/>
+      <c r="X12" s="4"/>
+      <c r="Y12" s="4"/>
+      <c r="Z12" s="4"/>
+      <c r="AA12" s="4"/>
       <c r="AB12" s="4"/>
       <c r="AC12" s="4"/>
       <c r="AD12" s="4"/>
@@ -1920,32 +1893,32 @@
     </row>
     <row r="13" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A13" s="14">
-        <v>341</v>
+        <v>412</v>
       </c>
       <c r="B13" s="14">
-        <v>13140161</v>
+        <v>12758063</v>
       </c>
       <c r="C13" s="5">
-        <v>7228507</v>
+        <v>4993371</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E13" s="14">
-        <v>43299316</v>
+        <v>43393460</v>
       </c>
       <c r="F13" s="14" t="s">
         <v>87</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="H13" s="6">
-        <v>46147</v>
+        <v>46172</v>
       </c>
       <c r="I13" s="13"/>
       <c r="J13" s="3">
-        <v>108</v>
+        <v>12</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1953,23 +1926,21 @@
       <c r="N13" s="4"/>
       <c r="O13" s="4"/>
       <c r="P13" s="4"/>
-      <c r="Q13" s="4">
-        <v>1</v>
-      </c>
+      <c r="Q13" s="4"/>
       <c r="R13" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S13" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T13" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U13" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V13" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W13" s="4"/>
       <c r="X13" s="4"/>
@@ -1994,50 +1965,74 @@
     </row>
     <row r="14" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A14" s="14">
-        <v>388</v>
+        <v>426</v>
       </c>
       <c r="B14" s="14">
-        <v>12757545</v>
+        <v>13263499</v>
       </c>
       <c r="C14" s="5">
-        <v>4993104</v>
+        <v>5274744</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>102</v>
       </c>
       <c r="E14" s="14">
-        <v>43389459</v>
+        <v>43395156</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="H14" s="6">
         <v>46147</v>
       </c>
       <c r="I14" s="13"/>
       <c r="J14" s="3">
-        <v>48</v>
+        <v>108</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
       <c r="N14" s="4"/>
       <c r="O14" s="4"/>
-      <c r="P14" s="4"/>
-      <c r="Q14" s="4"/>
-      <c r="R14" s="4"/>
-      <c r="S14" s="4"/>
-      <c r="T14" s="4"/>
-      <c r="U14" s="4"/>
-      <c r="V14" s="4"/>
-      <c r="W14" s="4"/>
-      <c r="X14" s="4"/>
-      <c r="Y14" s="4"/>
-      <c r="Z14" s="4"/>
-      <c r="AA14" s="4"/>
+      <c r="P14" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q14" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="R14" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="S14" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="T14" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="U14" s="4">
+        <v>1</v>
+      </c>
+      <c r="V14" s="4">
+        <v>2</v>
+      </c>
+      <c r="W14" s="4">
+        <v>3</v>
+      </c>
+      <c r="X14" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y14" s="4">
+        <v>2</v>
+      </c>
+      <c r="Z14" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA14" s="4" t="s">
+        <v>98</v>
+      </c>
       <c r="AB14" s="4"/>
       <c r="AC14" s="4"/>
       <c r="AD14" s="4"/>
@@ -2056,40 +2051,44 @@
     </row>
     <row r="15" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A15" s="14">
-        <v>390</v>
+        <v>427</v>
       </c>
       <c r="B15" s="14">
-        <v>12757893</v>
+        <v>13263552</v>
       </c>
       <c r="C15" s="5">
-        <v>4993255</v>
+        <v>7426389</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E15" s="14">
-        <v>43632407</v>
+        <v>43667419</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="H15" s="6">
-        <v>46172</v>
+        <v>46147</v>
       </c>
       <c r="I15" s="13"/>
       <c r="J15" s="3">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
       <c r="N15" s="4"/>
       <c r="O15" s="4"/>
-      <c r="P15" s="4"/>
-      <c r="Q15" s="4"/>
+      <c r="P15" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q15" s="4" t="s">
+        <v>98</v>
+      </c>
       <c r="R15" s="4">
         <v>1</v>
       </c>
@@ -2097,7 +2096,7 @@
         <v>2</v>
       </c>
       <c r="T15" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U15" s="4">
         <v>3</v>
@@ -2105,11 +2104,21 @@
       <c r="V15" s="4">
         <v>2</v>
       </c>
-      <c r="W15" s="4"/>
-      <c r="X15" s="4"/>
-      <c r="Y15" s="4"/>
-      <c r="Z15" s="4"/>
-      <c r="AA15" s="4"/>
+      <c r="W15" s="4">
+        <v>1</v>
+      </c>
+      <c r="X15" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="Y15" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z15" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA15" s="4" t="s">
+        <v>98</v>
+      </c>
       <c r="AB15" s="4"/>
       <c r="AC15" s="4"/>
       <c r="AD15" s="4"/>
@@ -2128,40 +2137,44 @@
     </row>
     <row r="16" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A16" s="14">
-        <v>409</v>
+        <v>429</v>
       </c>
       <c r="B16" s="14">
-        <v>12758052</v>
+        <v>13263489</v>
       </c>
       <c r="C16" s="5">
-        <v>4993370</v>
+        <v>5274747</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>102</v>
       </c>
       <c r="E16" s="14">
-        <v>43393460</v>
+        <v>43616206</v>
       </c>
       <c r="F16" s="14" t="s">
         <v>90</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="H16" s="6">
-        <v>46172</v>
+        <v>46147</v>
       </c>
       <c r="I16" s="13"/>
       <c r="J16" s="3">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
       <c r="N16" s="4"/>
       <c r="O16" s="4"/>
-      <c r="P16" s="4"/>
-      <c r="Q16" s="4"/>
+      <c r="P16" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q16" s="4" t="s">
+        <v>98</v>
+      </c>
       <c r="R16" s="4">
         <v>1</v>
       </c>
@@ -2169,7 +2182,7 @@
         <v>2</v>
       </c>
       <c r="T16" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U16" s="4">
         <v>3</v>
@@ -2177,11 +2190,21 @@
       <c r="V16" s="4">
         <v>2</v>
       </c>
-      <c r="W16" s="4"/>
-      <c r="X16" s="4"/>
-      <c r="Y16" s="4"/>
-      <c r="Z16" s="4"/>
-      <c r="AA16" s="4"/>
+      <c r="W16" s="4">
+        <v>1</v>
+      </c>
+      <c r="X16" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="Y16" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z16" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA16" s="4" t="s">
+        <v>98</v>
+      </c>
       <c r="AB16" s="4"/>
       <c r="AC16" s="4"/>
       <c r="AD16" s="4"/>
@@ -2200,40 +2223,44 @@
     </row>
     <row r="17" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A17" s="14">
-        <v>412</v>
+        <v>436</v>
       </c>
       <c r="B17" s="14">
-        <v>12758063</v>
+        <v>13263547</v>
       </c>
       <c r="C17" s="5">
-        <v>4993371</v>
+        <v>7426398</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E17" s="14">
-        <v>43393460</v>
+        <v>43927547</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="H17" s="6">
-        <v>46172</v>
+        <v>46178</v>
       </c>
       <c r="I17" s="13"/>
       <c r="J17" s="3">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
       <c r="N17" s="4"/>
       <c r="O17" s="4"/>
-      <c r="P17" s="4"/>
-      <c r="Q17" s="4"/>
+      <c r="P17" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q17" s="4" t="s">
+        <v>98</v>
+      </c>
       <c r="R17" s="4">
         <v>1</v>
       </c>
@@ -2241,7 +2268,7 @@
         <v>2</v>
       </c>
       <c r="T17" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U17" s="4">
         <v>3</v>
@@ -2249,11 +2276,21 @@
       <c r="V17" s="4">
         <v>2</v>
       </c>
-      <c r="W17" s="4"/>
-      <c r="X17" s="4"/>
-      <c r="Y17" s="4"/>
-      <c r="Z17" s="4"/>
-      <c r="AA17" s="4"/>
+      <c r="W17" s="4">
+        <v>1</v>
+      </c>
+      <c r="X17" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="Y17" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z17" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA17" s="4" t="s">
+        <v>98</v>
+      </c>
       <c r="AB17" s="4"/>
       <c r="AC17" s="4"/>
       <c r="AD17" s="4"/>
@@ -2272,32 +2309,32 @@
     </row>
     <row r="18" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A18" s="14">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="B18" s="14">
-        <v>13263497</v>
-      </c>
-      <c r="C18" s="18">
-        <v>5274744</v>
+        <v>13263549</v>
+      </c>
+      <c r="C18" s="5">
+        <v>7426399</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E18" s="14">
-        <v>43395156</v>
+        <v>43299316</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H18" s="6">
-        <v>46147</v>
+        <v>46178</v>
       </c>
       <c r="I18" s="13"/>
       <c r="J18" s="3">
-        <v>108</v>
+        <v>60</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -2305,40 +2342,40 @@
       <c r="N18" s="4"/>
       <c r="O18" s="4"/>
       <c r="P18" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="Q18" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="R18" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="S18" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="T18" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
+      </c>
+      <c r="R18" s="4">
+        <v>1</v>
+      </c>
+      <c r="S18" s="4">
+        <v>2</v>
+      </c>
+      <c r="T18" s="4">
+        <v>3</v>
       </c>
       <c r="U18" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V18" s="4">
         <v>2</v>
       </c>
       <c r="W18" s="4">
-        <v>3</v>
-      </c>
-      <c r="X18" s="4">
-        <v>3</v>
-      </c>
-      <c r="Y18" s="4">
-        <v>2</v>
-      </c>
-      <c r="Z18" s="4">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="X18" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="Y18" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z18" s="4" t="s">
+        <v>98</v>
       </c>
       <c r="AA18" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="AB18" s="4"/>
       <c r="AC18" s="4"/>
@@ -2358,28 +2395,28 @@
     </row>
     <row r="19" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A19" s="14">
-        <v>427</v>
+        <v>442</v>
       </c>
       <c r="B19" s="16">
-        <v>12265544</v>
+        <v>13263498</v>
       </c>
       <c r="C19" s="17">
-        <v>5348675</v>
+        <v>5274759</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E19" s="14">
-        <v>43667419</v>
+        <v>43263432</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H19" s="6">
-        <v>46147</v>
+        <v>46178</v>
       </c>
       <c r="I19" s="13"/>
       <c r="J19" s="3">
@@ -2391,10 +2428,10 @@
       <c r="N19" s="4"/>
       <c r="O19" s="4"/>
       <c r="P19" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="Q19" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="R19" s="4">
         <v>1</v>
@@ -2415,16 +2452,16 @@
         <v>1</v>
       </c>
       <c r="X19" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="Y19" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="Z19" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="AA19" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="AB19" s="4"/>
       <c r="AC19" s="4"/>
@@ -2444,25 +2481,25 @@
     </row>
     <row r="20" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A20" s="14">
-        <v>429</v>
+        <v>443</v>
       </c>
       <c r="B20" s="14">
-        <v>13263489</v>
+        <v>13263561</v>
       </c>
       <c r="C20" s="5">
-        <v>5274747</v>
+        <v>7426391</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E20" s="14">
-        <v>43616206</v>
+        <v>43299316</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="H20" s="6">
         <v>46147</v>
@@ -2477,10 +2514,10 @@
       <c r="N20" s="4"/>
       <c r="O20" s="4"/>
       <c r="P20" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="Q20" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="R20" s="4">
         <v>1</v>
@@ -2501,16 +2538,16 @@
         <v>1</v>
       </c>
       <c r="X20" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="Y20" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="Z20" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="AA20" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="AB20" s="4"/>
       <c r="AC20" s="4"/>
@@ -2530,19 +2567,19 @@
     </row>
     <row r="21" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A21" s="14">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="B21" s="14">
-        <v>13263547</v>
+        <v>13263493</v>
       </c>
       <c r="C21" s="5">
-        <v>7426398</v>
+        <v>5274761</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E21" s="14">
-        <v>43927547</v>
+        <v>43772253</v>
       </c>
       <c r="F21" s="14" t="s">
         <v>95</v>
@@ -2555,49 +2592,37 @@
       </c>
       <c r="I21" s="13"/>
       <c r="J21" s="3">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
       <c r="M21" s="4"/>
-      <c r="N21" s="4"/>
-      <c r="O21" s="4"/>
-      <c r="P21" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q21" s="4" t="s">
-        <v>101</v>
+      <c r="N21" s="4">
+        <v>1</v>
+      </c>
+      <c r="O21" s="4">
+        <v>1</v>
+      </c>
+      <c r="P21" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q21" s="4">
+        <v>2</v>
       </c>
       <c r="R21" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S21" s="4">
-        <v>2</v>
-      </c>
-      <c r="T21" s="4">
-        <v>3</v>
-      </c>
-      <c r="U21" s="4">
-        <v>3</v>
-      </c>
-      <c r="V21" s="4">
-        <v>2</v>
-      </c>
-      <c r="W21" s="4">
-        <v>1</v>
-      </c>
-      <c r="X21" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="Y21" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="Z21" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="AA21" s="4" t="s">
-        <v>101</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="T21" s="4"/>
+      <c r="U21" s="4"/>
+      <c r="V21" s="4"/>
+      <c r="W21" s="4"/>
+      <c r="X21" s="4"/>
+      <c r="Y21" s="4"/>
+      <c r="Z21" s="4"/>
+      <c r="AA21" s="4"/>
       <c r="AB21" s="4"/>
       <c r="AC21" s="4"/>
       <c r="AD21" s="4"/>
@@ -2616,32 +2641,32 @@
     </row>
     <row r="22" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A22" s="14">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="B22" s="14">
-        <v>13263549</v>
+        <v>13263487</v>
       </c>
       <c r="C22" s="5">
-        <v>7426399</v>
+        <v>5274754</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E22" s="14">
-        <v>43299316</v>
+        <v>43616206</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="H22" s="6">
-        <v>46178</v>
+        <v>46147</v>
       </c>
       <c r="I22" s="13"/>
       <c r="J22" s="3">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -2649,10 +2674,10 @@
       <c r="N22" s="4"/>
       <c r="O22" s="4"/>
       <c r="P22" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="Q22" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="R22" s="4">
         <v>1</v>
@@ -2673,16 +2698,16 @@
         <v>1</v>
       </c>
       <c r="X22" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="Y22" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="Z22" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="AA22" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="AB22" s="4"/>
       <c r="AC22" s="4"/>
@@ -2702,73 +2727,61 @@
     </row>
     <row r="23" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A23" s="14">
-        <v>442</v>
+        <v>483</v>
       </c>
       <c r="B23" s="14">
-        <v>13263498</v>
+        <v>13175375</v>
       </c>
       <c r="C23" s="5">
-        <v>5274759</v>
+        <v>5240742</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>102</v>
       </c>
       <c r="E23" s="14">
-        <v>43263432</v>
+        <v>43342471</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="G23" s="14" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="H23" s="6">
-        <v>46178</v>
+        <v>46113</v>
       </c>
       <c r="I23" s="13"/>
       <c r="J23" s="3">
-        <v>36</v>
+        <v>156</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
       <c r="M23" s="4"/>
       <c r="N23" s="4"/>
       <c r="O23" s="4"/>
-      <c r="P23" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q23" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="R23" s="4">
-        <v>1</v>
-      </c>
-      <c r="S23" s="4">
-        <v>2</v>
-      </c>
-      <c r="T23" s="4">
-        <v>3</v>
-      </c>
-      <c r="U23" s="4">
-        <v>3</v>
-      </c>
+      <c r="P23" s="4"/>
+      <c r="Q23" s="4"/>
+      <c r="R23" s="4"/>
+      <c r="S23" s="4"/>
+      <c r="T23" s="4"/>
+      <c r="U23" s="4"/>
       <c r="V23" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W23" s="4">
-        <v>1</v>
-      </c>
-      <c r="X23" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="Y23" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="Z23" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="AA23" s="4" t="s">
-        <v>101</v>
+        <v>2</v>
+      </c>
+      <c r="X23" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y23" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z23" s="4">
+        <v>2</v>
+      </c>
+      <c r="AA23" s="4">
+        <v>1</v>
       </c>
       <c r="AB23" s="4"/>
       <c r="AC23" s="4"/>
@@ -2788,73 +2801,61 @@
     </row>
     <row r="24" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A24" s="14">
-        <v>443</v>
+        <v>484</v>
       </c>
       <c r="B24" s="14">
-        <v>13263561</v>
+        <v>13175377</v>
       </c>
       <c r="C24" s="5">
-        <v>7426391</v>
+        <v>5240741</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E24" s="14">
-        <v>43299316</v>
+        <v>43342471</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="H24" s="6">
-        <v>46147</v>
+        <v>46113</v>
       </c>
       <c r="I24" s="13"/>
       <c r="J24" s="3">
-        <v>48</v>
+        <v>192</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
       <c r="M24" s="4"/>
       <c r="N24" s="4"/>
       <c r="O24" s="4"/>
-      <c r="P24" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q24" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="R24" s="4">
-        <v>1</v>
-      </c>
-      <c r="S24" s="4">
-        <v>2</v>
-      </c>
-      <c r="T24" s="4">
-        <v>3</v>
-      </c>
-      <c r="U24" s="4">
-        <v>3</v>
-      </c>
+      <c r="P24" s="4"/>
+      <c r="Q24" s="4"/>
+      <c r="R24" s="4"/>
+      <c r="S24" s="4"/>
+      <c r="T24" s="4"/>
+      <c r="U24" s="4"/>
       <c r="V24" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W24" s="4">
-        <v>1</v>
-      </c>
-      <c r="X24" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="Y24" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="Z24" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="AA24" s="4" t="s">
-        <v>101</v>
+        <v>2</v>
+      </c>
+      <c r="X24" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y24" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z24" s="4">
+        <v>2</v>
+      </c>
+      <c r="AA24" s="4">
+        <v>1</v>
       </c>
       <c r="AB24" s="4"/>
       <c r="AC24" s="4"/>
@@ -2874,62 +2875,62 @@
     </row>
     <row r="25" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A25" s="14">
-        <v>446</v>
+        <v>485</v>
       </c>
       <c r="B25" s="14">
-        <v>13263493</v>
+        <v>13175378</v>
       </c>
       <c r="C25" s="5">
-        <v>5274761</v>
+        <v>5240740</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>102</v>
       </c>
       <c r="E25" s="14">
-        <v>43772253</v>
+        <v>43342471</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G25" s="14" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H25" s="6">
-        <v>46178</v>
+        <v>46113</v>
       </c>
       <c r="I25" s="13"/>
       <c r="J25" s="3">
-        <v>36</v>
+        <v>360</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
       <c r="M25" s="4"/>
-      <c r="N25" s="4">
-        <v>1</v>
-      </c>
-      <c r="O25" s="4">
-        <v>1</v>
-      </c>
-      <c r="P25" s="4">
-        <v>2</v>
-      </c>
-      <c r="Q25" s="4">
-        <v>2</v>
-      </c>
-      <c r="R25" s="4">
-        <v>3</v>
-      </c>
-      <c r="S25" s="4">
-        <v>3</v>
-      </c>
+      <c r="N25" s="4"/>
+      <c r="O25" s="4"/>
+      <c r="P25" s="4"/>
+      <c r="Q25" s="4"/>
+      <c r="R25" s="4"/>
+      <c r="S25" s="4"/>
       <c r="T25" s="4"/>
       <c r="U25" s="4"/>
-      <c r="V25" s="4"/>
-      <c r="W25" s="4"/>
-      <c r="X25" s="4"/>
-      <c r="Y25" s="4"/>
-      <c r="Z25" s="4"/>
-      <c r="AA25" s="4"/>
+      <c r="V25" s="4">
+        <v>1</v>
+      </c>
+      <c r="W25" s="4">
+        <v>2</v>
+      </c>
+      <c r="X25" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y25" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z25" s="4">
+        <v>2</v>
+      </c>
+      <c r="AA25" s="4">
+        <v>1</v>
+      </c>
       <c r="AB25" s="4"/>
       <c r="AC25" s="4"/>
       <c r="AD25" s="4"/>
@@ -2948,73 +2949,61 @@
     </row>
     <row r="26" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A26" s="14">
-        <v>447</v>
+        <v>486</v>
       </c>
       <c r="B26" s="14">
-        <v>13263487</v>
+        <v>13185973</v>
       </c>
       <c r="C26" s="5">
-        <v>5274754</v>
+        <v>5245130</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>102</v>
       </c>
       <c r="E26" s="14">
-        <v>43616206</v>
+        <v>43342471</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H26" s="6">
-        <v>46147</v>
+        <v>46132</v>
       </c>
       <c r="I26" s="13"/>
       <c r="J26" s="3">
-        <v>48</v>
+        <v>108</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
       <c r="M26" s="4"/>
       <c r="N26" s="4"/>
       <c r="O26" s="4"/>
-      <c r="P26" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q26" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="R26" s="4">
-        <v>1</v>
-      </c>
-      <c r="S26" s="4">
-        <v>2</v>
-      </c>
-      <c r="T26" s="4">
-        <v>3</v>
-      </c>
-      <c r="U26" s="4">
-        <v>3</v>
-      </c>
+      <c r="P26" s="4"/>
+      <c r="Q26" s="4"/>
+      <c r="R26" s="4"/>
+      <c r="S26" s="4"/>
+      <c r="T26" s="4"/>
+      <c r="U26" s="4"/>
       <c r="V26" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W26" s="4">
-        <v>1</v>
-      </c>
-      <c r="X26" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="Y26" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="Z26" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="AA26" s="4" t="s">
-        <v>101</v>
+        <v>2</v>
+      </c>
+      <c r="X26" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y26" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z26" s="4">
+        <v>2</v>
+      </c>
+      <c r="AA26" s="4">
+        <v>1</v>
       </c>
       <c r="AB26" s="4"/>
       <c r="AC26" s="4"/>
@@ -3039,10 +3028,79 @@
       <c r="C28" s="12"/>
     </row>
     <row r="29" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="C29" s="12"/>
+      <c r="C29" s="18"/>
     </row>
     <row r="30" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="C30" s="12"/>
+      <c r="C30" s="18"/>
+    </row>
+    <row r="31" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="C31" s="18"/>
+    </row>
+    <row r="32" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="C32" s="18"/>
+    </row>
+    <row r="33" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C33" s="18"/>
+    </row>
+    <row r="34" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C34" s="18"/>
+    </row>
+    <row r="35" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C35" s="18"/>
+    </row>
+    <row r="36" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C36" s="18"/>
+    </row>
+    <row r="37" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C37" s="18"/>
+    </row>
+    <row r="38" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C38" s="18"/>
+    </row>
+    <row r="39" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C39" s="18"/>
+    </row>
+    <row r="40" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C40" s="18"/>
+    </row>
+    <row r="41" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C41" s="18"/>
+    </row>
+    <row r="42" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C42" s="18"/>
+    </row>
+    <row r="43" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C43" s="18"/>
+    </row>
+    <row r="44" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C44" s="18"/>
+    </row>
+    <row r="45" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C45" s="18"/>
+    </row>
+    <row r="46" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C46" s="18"/>
+    </row>
+    <row r="47" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C47" s="18"/>
+    </row>
+    <row r="48" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C48" s="18"/>
+    </row>
+    <row r="49" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C49" s="18"/>
+    </row>
+    <row r="50" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C50" s="18"/>
+    </row>
+    <row r="51" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C51" s="18"/>
+    </row>
+    <row r="52" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C52" s="18"/>
+    </row>
+    <row r="53" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C53" s="18"/>
     </row>
   </sheetData>
   <autoFilter ref="B1:AA26" xr:uid="{D63AD4AA-E078-4C28-AB28-3D04A26ABB28}"/>

--- a/DISPO.xlsx
+++ b/DISPO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{300C0672-1416-4AF0-B213-79BF21725C6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2695DA8E-1F12-4C5D-8E20-B54149497DF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{D5233C47-2897-4F0E-9138-F4B2B2ED9B28}"/>
   </bookViews>
@@ -351,7 +351,7 @@
     <t>VULTS</t>
   </si>
   <si>
-    <t>PREV. FAT.</t>
+    <t>DATA ENTREGA</t>
   </si>
 </sst>
 </file>

--- a/DISPO.xlsx
+++ b/DISPO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D4188BA-B77C-4A0D-80C9-5013242D1E4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7A0BBA7-55C7-4DA2-93DB-5830662AFCFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{D5233C47-2897-4F0E-9138-F4B2B2ED9B28}"/>
   </bookViews>
@@ -3041,7 +3041,7 @@
         <v>93</v>
       </c>
       <c r="H27" s="6">
-        <v>46178</v>
+        <v>46147</v>
       </c>
       <c r="I27" s="12"/>
       <c r="J27" s="3">
